--- a/data-raw/questionnaires/Instrumente_2025-02-22_Seb_final.xlsx
+++ b/data-raw/questionnaires/Instrumente_2025-02-22_Seb_final.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10309"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sebsilas/songbird/data-raw/questionnaires/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{527F0E77-EF02-5B4A-B32D-AFA88A122616}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8B11244-A777-424C-A5CD-BB23FACC120B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2800" yWindow="1460" windowWidth="33800" windowHeight="19720" tabRatio="730" activeTab="2" xr2:uid="{186B0E8D-C293-E64A-BB14-A06646A98239}"/>
+    <workbookView xWindow="740" yWindow="1460" windowWidth="33800" windowHeight="19720" tabRatio="730" xr2:uid="{186B0E8D-C293-E64A-BB14-A06646A98239}"/>
   </bookViews>
   <sheets>
     <sheet name="Items_Kinder" sheetId="5" r:id="rId1"/>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1330" uniqueCount="661">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1327" uniqueCount="660">
   <si>
     <t>Konstrukt</t>
   </si>
@@ -667,12 +667,6 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">1 = nie; 2 = einmal pro Jahr; 3 = 2- bis 3-mal pro Jahr; 4 = mehr als 3-mal pro Jahr  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 = nein; 2 = selten; 3 = meistens; 4 = immer </t>
-  </si>
-  <si>
     <t xml:space="preserve">Wir besitzen daheim viele Tonträger (z. B. Audio-CDs oder Schallplatten). </t>
   </si>
   <si>
@@ -898,16 +892,10 @@
     <t>Musikpraktische Vorkenntnisse</t>
   </si>
   <si>
-    <t>Falls du kein Instrument spielst: Ich kann beurteilen, ob jemand anderes sein Instrument richtig spielt. </t>
-  </si>
-  <si>
     <t>Ich kann beurteilen, ob ich richtig singe. </t>
   </si>
   <si>
     <t>Ich kann beurteilen, ob jemand anderes richtig singt. </t>
-  </si>
-  <si>
-    <t>Ich kann beurteilen, ob ich mein Instrument richtig spiele. </t>
   </si>
   <si>
     <t>Familiäre Musikpraxis</t>
@@ -1311,9 +1299,6 @@
   </si>
   <si>
     <t>Unsere Singleiterin/unser Singleiter ist geduldig, wenn jemand im Unterricht einen Fehler macht.</t>
-  </si>
-  <si>
-    <t>Bei unserer Singleiterin/unsem Singleiter ist Fehlermachen nichts Schlimmes.</t>
   </si>
   <si>
     <t>Unsere Singleiterin/unser Singleiter achtet darauf, dass in unserer Klasse niemand ausgelacht wird, der einen Fehler macht.</t>
@@ -2115,9 +2100,6 @@
     <t>Welche berufliche Ausbildung hat der andere Erziehungsberechtigte?</t>
   </si>
   <si>
-    <t>4;5;6;7;8</t>
-  </si>
-  <si>
     <t>Afghanistan; Bosnien und Herzegowina; Bulgarien; Deutschland; Frankreich; Griechenland; Indien; Irak; Italien; Kosovo; Kroatien; Österreich; Polen; Portugal; Rumänien; Russland; Serbien; Spanien; Syrien; Türkei; Ungarn; anderes Land</t>
   </si>
   <si>
@@ -2133,15 +2115,9 @@
     <t>Berufliche Stellung</t>
   </si>
   <si>
-    <t>1=Ich habe ein künstlerisches oder pädagogisches Instrumentalstudium absolviert.;2=Ich habe ein künstlerisches oder pädagogisches Gesangsstudium absolviert.;3=Ich habe Kirchenmusik studiert.;4=Ich habe ein Lehramtsstudium mit Hauptfach Musik absolviert.;5=Ich habe ein anderes musikbezogenes Studium absolviert:;6=Welches?;7=Ich bin Chorleiter:in.;9=Ich mache in meiner Freizeit viel Musik.;10=Ich spiele ein Instrument.;11=Ich singe im Chor.;12=Ich habe einen anderen Zugang zu Musik, und zwar:;13=Welchen?</t>
-  </si>
-  <si>
     <t>Jonkmann, K., Rose, N. &amp; Trautwein, U. (2013)</t>
   </si>
   <si>
-    <t>4;5;6;7;8;9;10;11;12;13;14;15;16;17;18;19;20;21;22;23;24;25;26;27;28;29;30;31;32;33;34;35;36;37;38;39;40;41;42;43;44;45;46;47;48;49;50;51;52;53;54;55;56;57;58;59;60;61;62;63;64;65;66;67;68;69;70;71;72;73;74;75;76;77;78;79;80;81;82;83;84;85;86;87;88;89;90;91;92;93;94;95;96;97;98;99;100</t>
-  </si>
-  <si>
     <t xml:space="preserve">Schulabschluss </t>
   </si>
   <si>
@@ -2155,6 +2131,27 @@
   </si>
   <si>
     <t>weniger als 1 Jahr; 1–2 Jahre; 3–4 Jahre; 5–9 Jahre; 10–14 Jahre; mehr als 15 Jahre</t>
+  </si>
+  <si>
+    <t>1=Nie; 2=Einmal pro Jahr; 3=Zwei- bis dreimal pro Jahr; 4=Mehr als dreimal pro Jahr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 = Nein; 2 = Selten; 3 = Meistens; 4 = Immer </t>
+  </si>
+  <si>
+    <t>18;19;20;21;22;23;24;25;26;27;28;29;30;31;32;33;34;35;36;37;38;39;40;41;42;43;44;45;46;47;48;49;50;51;52;53;54;55;56;57;58;59;60;61;62;63;64;65;66;67;68;69;70;71;72;73;74;75;76;77;78;79;80;81;82;83;84;85;86;87;88;89;90;91;92;93;94;95;96;97;98;99;100</t>
+  </si>
+  <si>
+    <t>1=Ich habe ein künstlerisches oder pädagogisches Instrumentalstudium absolviert.;2=Ich habe ein künstlerisches oder pädagogisches Gesangsstudium absolviert.;3=Ich habe Kirchenmusik studiert.;4=Ich habe ein Lehramtsstudium mit Hauptfach Musik absolviert.;5=Ich habe ein anderes musikbezogenes Studium absolviert:;6=Ich bin Chorleiter:in.;7=Ich mache in meiner Freizeit viel Musik.;8=Ich spiele ein Instrument.;9=Ich singe im Chor.;10=Ich habe einen anderen Zugang zu Musik, und zwar:</t>
+  </si>
+  <si>
+    <t>Bei unserer Singleiterin/unserem Singleiter ist Fehlermachen nichts Schlimmes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ich kann beurteilen, ob ich mein Instrument richtig spiele. Falls du kein Instrument spielst: Ich kann beurteilen, ob jemand anderes sein Instrument richtig spielt. </t>
+  </si>
+  <si>
+    <t>7;8;9;10;11;12;13</t>
   </si>
 </sst>
 </file>
@@ -2635,8 +2632,14 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -2656,19 +2659,13 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -3028,7 +3025,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J74"/>
+  <dimension ref="A1:J73"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="19.33203125" style="61" customWidth="1"/>
@@ -3043,21 +3040,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="34.5" customHeight="1">
-      <c r="A1" s="81" t="s">
-        <v>346</v>
-      </c>
-      <c r="B1" s="81"/>
-      <c r="C1" s="81"/>
-      <c r="D1" s="81"/>
-      <c r="E1" s="81"/>
-      <c r="F1" s="81"/>
-      <c r="G1" s="81"/>
-      <c r="H1" s="81"/>
-      <c r="I1" s="81"/>
+      <c r="A1" s="90" t="s">
+        <v>342</v>
+      </c>
+      <c r="B1" s="90"/>
+      <c r="C1" s="90"/>
+      <c r="D1" s="90"/>
+      <c r="E1" s="90"/>
+      <c r="F1" s="90"/>
+      <c r="G1" s="90"/>
+      <c r="H1" s="90"/>
+      <c r="I1" s="90"/>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="48" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="B2" s="31" t="s">
         <v>0</v>
@@ -3085,7 +3082,7 @@
       </c>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3" s="88" t="s">
+      <c r="A3" s="91" t="s">
         <v>50</v>
       </c>
       <c r="B3" s="32" t="s">
@@ -3097,17 +3094,17 @@
       </c>
       <c r="F3" s="34"/>
       <c r="G3" s="33" t="s">
-        <v>637</v>
+        <v>632</v>
       </c>
       <c r="H3" s="74" t="s">
-        <v>647</v>
+        <v>659</v>
       </c>
       <c r="I3" s="33" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="4" spans="1:9" s="42" customFormat="1">
-      <c r="A4" s="89"/>
+      <c r="A4" s="92"/>
       <c r="B4" s="63" t="s">
         <v>41</v>
       </c>
@@ -3120,21 +3117,21 @@
         <v>62</v>
       </c>
       <c r="H4" s="44" t="s">
-        <v>636</v>
+        <v>631</v>
       </c>
       <c r="I4" s="43" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
     </row>
     <row r="5" spans="1:9" s="23" customFormat="1" ht="15">
-      <c r="A5" s="90" t="s">
-        <v>331</v>
+      <c r="A5" s="81" t="s">
+        <v>327</v>
       </c>
       <c r="B5" s="33" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C5" s="33" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D5" s="33" t="s">
         <v>125</v>
@@ -3144,16 +3141,16 @@
       <c r="G5" s="33"/>
       <c r="H5" s="35"/>
       <c r="I5" s="35" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
     </row>
     <row r="6" spans="1:9" s="45" customFormat="1" ht="15">
-      <c r="A6" s="91"/>
+      <c r="A6" s="82"/>
       <c r="B6" s="43" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="C6" s="40" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D6" s="40" t="s">
         <v>125</v>
@@ -3165,12 +3162,12 @@
       <c r="I6" s="40"/>
     </row>
     <row r="7" spans="1:9">
-      <c r="A7" s="91"/>
+      <c r="A7" s="82"/>
       <c r="B7" s="33" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="C7" s="35" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="D7" s="35" t="s">
         <v>125</v>
@@ -3182,12 +3179,12 @@
       <c r="I7" s="35"/>
     </row>
     <row r="8" spans="1:9" s="42" customFormat="1">
-      <c r="A8" s="92"/>
+      <c r="A8" s="83"/>
       <c r="B8" s="43" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="C8" s="40" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="D8" s="40" t="s">
         <v>125</v>
@@ -3199,14 +3196,14 @@
       <c r="I8" s="40"/>
     </row>
     <row r="9" spans="1:9">
-      <c r="A9" s="90" t="s">
-        <v>263</v>
-      </c>
-      <c r="B9" s="82" t="s">
+      <c r="A9" s="81" t="s">
+        <v>261</v>
+      </c>
+      <c r="B9" s="84" t="s">
         <v>48</v>
       </c>
       <c r="C9" s="35" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D9" s="35" t="s">
         <v>125</v>
@@ -3215,45 +3212,45 @@
       <c r="F9" s="35"/>
       <c r="G9" s="35"/>
       <c r="H9" s="35" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="I9" s="35" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:9">
-      <c r="A10" s="91"/>
-      <c r="B10" s="83"/>
+      <c r="A10" s="82"/>
+      <c r="B10" s="85"/>
       <c r="C10" s="35"/>
       <c r="D10" s="35"/>
       <c r="E10" s="35"/>
       <c r="F10" s="35"/>
       <c r="G10" s="35"/>
       <c r="H10" s="35" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="I10" s="35" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:9">
-      <c r="A11" s="91"/>
-      <c r="B11" s="84"/>
+      <c r="A11" s="82"/>
+      <c r="B11" s="86"/>
       <c r="C11" s="35"/>
       <c r="D11" s="35"/>
       <c r="E11" s="35"/>
       <c r="F11" s="35"/>
       <c r="G11" s="35"/>
       <c r="H11" s="35" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="I11" s="35" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="12" spans="1:9" s="42" customFormat="1">
-      <c r="A12" s="91"/>
-      <c r="B12" s="85" t="s">
+      <c r="A12" s="82"/>
+      <c r="B12" s="87" t="s">
         <v>45</v>
       </c>
       <c r="C12" s="40"/>
@@ -3262,45 +3259,45 @@
       <c r="F12" s="41"/>
       <c r="G12" s="40"/>
       <c r="H12" s="40" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="I12" s="40" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="13" spans="1:9" s="42" customFormat="1">
-      <c r="A13" s="91"/>
-      <c r="B13" s="86"/>
+      <c r="A13" s="82"/>
+      <c r="B13" s="88"/>
       <c r="C13" s="40"/>
       <c r="D13" s="40"/>
       <c r="E13" s="40"/>
       <c r="F13" s="41"/>
       <c r="G13" s="40"/>
       <c r="H13" s="40" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="I13" s="40" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="14" spans="1:9" s="42" customFormat="1">
-      <c r="A14" s="91"/>
-      <c r="B14" s="87"/>
+      <c r="A14" s="82"/>
+      <c r="B14" s="89"/>
       <c r="C14" s="40"/>
       <c r="D14" s="40"/>
       <c r="E14" s="40"/>
       <c r="F14" s="41"/>
       <c r="G14" s="40"/>
       <c r="H14" s="40" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="I14" s="40" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="15" spans="1:9">
-      <c r="A15" s="91"/>
-      <c r="B15" s="82" t="s">
+      <c r="A15" s="82"/>
+      <c r="B15" s="84" t="s">
         <v>46</v>
       </c>
       <c r="C15" s="35"/>
@@ -3308,43 +3305,43 @@
       <c r="E15" s="35"/>
       <c r="G15" s="35"/>
       <c r="H15" s="35" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="I15" s="35" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="16" spans="1:9">
-      <c r="A16" s="91"/>
-      <c r="B16" s="83"/>
+      <c r="A16" s="82"/>
+      <c r="B16" s="85"/>
       <c r="C16" s="35"/>
       <c r="D16" s="35"/>
       <c r="E16" s="35"/>
       <c r="G16" s="35"/>
       <c r="H16" s="35" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="I16" s="35" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="17" spans="1:10">
-      <c r="A17" s="91"/>
-      <c r="B17" s="84"/>
+      <c r="A17" s="82"/>
+      <c r="B17" s="86"/>
       <c r="C17" s="35"/>
       <c r="D17" s="35"/>
       <c r="E17" s="35"/>
       <c r="G17" s="35"/>
       <c r="H17" s="35" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="I17" s="35" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="18" spans="1:10" s="42" customFormat="1">
-      <c r="A18" s="91"/>
-      <c r="B18" s="85" t="s">
+      <c r="A18" s="82"/>
+      <c r="B18" s="87" t="s">
         <v>47</v>
       </c>
       <c r="C18" s="40"/>
@@ -3353,48 +3350,48 @@
       <c r="F18" s="41"/>
       <c r="G18" s="40"/>
       <c r="H18" s="40" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="I18" s="40" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="19" spans="1:10" s="42" customFormat="1">
-      <c r="A19" s="91"/>
-      <c r="B19" s="86"/>
+      <c r="A19" s="82"/>
+      <c r="B19" s="88"/>
       <c r="C19" s="40"/>
       <c r="D19" s="40"/>
       <c r="E19" s="40"/>
       <c r="F19" s="40"/>
       <c r="G19" s="40"/>
       <c r="H19" s="40" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="I19" s="40" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="20" spans="1:10" s="42" customFormat="1">
-      <c r="A20" s="92"/>
-      <c r="B20" s="87"/>
+      <c r="A20" s="83"/>
+      <c r="B20" s="89"/>
       <c r="C20" s="40"/>
       <c r="D20" s="40"/>
       <c r="E20" s="40"/>
       <c r="F20" s="40"/>
       <c r="G20" s="40"/>
       <c r="H20" s="40" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="I20" s="40" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="21" spans="1:10">
-      <c r="A21" s="90" t="s">
-        <v>332</v>
-      </c>
-      <c r="B21" s="82" t="s">
-        <v>252</v>
+      <c r="A21" s="81" t="s">
+        <v>328</v>
+      </c>
+      <c r="B21" s="84" t="s">
+        <v>250</v>
       </c>
       <c r="C21" s="35" t="s">
         <v>49</v>
@@ -3408,15 +3405,15 @@
         <v>62</v>
       </c>
       <c r="H21" s="35" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="I21" s="35" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
     </row>
     <row r="22" spans="1:10">
-      <c r="A22" s="91"/>
-      <c r="B22" s="83"/>
+      <c r="A22" s="82"/>
+      <c r="B22" s="85"/>
       <c r="C22" s="35"/>
       <c r="D22" s="35" t="s">
         <v>125</v>
@@ -3427,15 +3424,15 @@
         <v>62</v>
       </c>
       <c r="H22" s="35" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="I22" s="35" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
     </row>
     <row r="23" spans="1:10">
-      <c r="A23" s="91"/>
-      <c r="B23" s="84"/>
+      <c r="A23" s="82"/>
+      <c r="B23" s="86"/>
       <c r="C23" s="39"/>
       <c r="D23" s="39" t="s">
         <v>125</v>
@@ -3446,26 +3443,26 @@
         <v>62</v>
       </c>
       <c r="H23" s="39" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="I23" s="39" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
     </row>
     <row r="24" spans="1:10" s="42" customFormat="1">
-      <c r="A24" s="91"/>
+      <c r="A24" s="82"/>
       <c r="B24" s="63" t="s">
+        <v>266</v>
+      </c>
+      <c r="C24" s="46" t="s">
         <v>268</v>
-      </c>
-      <c r="C24" s="46" t="s">
-        <v>270</v>
       </c>
       <c r="D24" s="46" t="s">
         <v>125</v>
       </c>
       <c r="E24" s="46"/>
       <c r="F24" s="46" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G24" s="46" t="s">
         <v>63</v>
@@ -3474,11 +3471,11 @@
         <v>63</v>
       </c>
       <c r="I24" s="46" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
     </row>
     <row r="25" spans="1:10">
-      <c r="A25" s="91"/>
+      <c r="A25" s="82"/>
       <c r="B25" s="33"/>
       <c r="C25" s="39"/>
       <c r="D25" s="39"/>
@@ -3488,14 +3485,14 @@
         <v>62</v>
       </c>
       <c r="H25" s="39" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="I25" s="39" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="26" spans="1:10" s="42" customFormat="1">
-      <c r="A26" s="91"/>
+      <c r="A26" s="82"/>
       <c r="B26" s="43"/>
       <c r="C26" s="40"/>
       <c r="D26" s="40"/>
@@ -3505,15 +3502,15 @@
         <v>62</v>
       </c>
       <c r="H26" s="46" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="I26" s="40" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="J26" s="47"/>
     </row>
     <row r="27" spans="1:10" s="42" customFormat="1">
-      <c r="A27" s="91"/>
+      <c r="A27" s="82"/>
       <c r="B27" s="43"/>
       <c r="C27" s="40"/>
       <c r="D27" s="40"/>
@@ -3523,17 +3520,17 @@
         <v>62</v>
       </c>
       <c r="H27" s="40" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="I27" s="40" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="J27" s="47"/>
     </row>
     <row r="28" spans="1:10">
-      <c r="A28" s="91"/>
-      <c r="B28" s="82" t="s">
-        <v>274</v>
+      <c r="A28" s="82"/>
+      <c r="B28" s="84" t="s">
+        <v>272</v>
       </c>
       <c r="C28" s="35" t="s">
         <v>43</v>
@@ -3547,16 +3544,16 @@
         <v>62</v>
       </c>
       <c r="H28" s="35" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="I28" s="35" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="J28" s="4"/>
     </row>
     <row r="29" spans="1:10">
-      <c r="A29" s="91"/>
-      <c r="B29" s="83"/>
+      <c r="A29" s="82"/>
+      <c r="B29" s="85"/>
       <c r="C29" s="35"/>
       <c r="D29" s="35"/>
       <c r="E29" s="35"/>
@@ -3565,16 +3562,16 @@
         <v>62</v>
       </c>
       <c r="H29" s="35" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="I29" s="35" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="J29" s="4"/>
     </row>
     <row r="30" spans="1:10">
-      <c r="A30" s="91"/>
-      <c r="B30" s="83"/>
+      <c r="A30" s="82"/>
+      <c r="B30" s="85"/>
       <c r="C30" s="35"/>
       <c r="D30" s="35"/>
       <c r="E30" s="35"/>
@@ -3583,58 +3580,58 @@
         <v>62</v>
       </c>
       <c r="H30" s="35" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="I30" s="35" t="s">
-        <v>278</v>
+        <v>658</v>
       </c>
       <c r="J30" s="4"/>
     </row>
-    <row r="31" spans="1:10">
-      <c r="A31" s="91"/>
-      <c r="B31" s="84"/>
-      <c r="C31" s="35"/>
-      <c r="D31" s="35"/>
-      <c r="E31" s="35"/>
-      <c r="F31" s="35"/>
-      <c r="G31" s="35" t="s">
+    <row r="31" spans="1:10" s="42" customFormat="1">
+      <c r="A31" s="82"/>
+      <c r="B31" s="87" t="s">
+        <v>275</v>
+      </c>
+      <c r="C31" s="40" t="s">
+        <v>44</v>
+      </c>
+      <c r="D31" s="46" t="s">
+        <v>314</v>
+      </c>
+      <c r="E31" s="40"/>
+      <c r="F31" s="40"/>
+      <c r="G31" s="40" t="s">
         <v>62</v>
       </c>
-      <c r="H31" s="35" t="s">
-        <v>317</v>
-      </c>
-      <c r="I31" s="35" t="s">
-        <v>275</v>
-      </c>
-      <c r="J31" s="4"/>
+      <c r="H31" s="40" t="s">
+        <v>313</v>
+      </c>
+      <c r="I31" s="40" t="s">
+        <v>276</v>
+      </c>
+      <c r="J31" s="47"/>
     </row>
     <row r="32" spans="1:10" s="42" customFormat="1">
-      <c r="A32" s="91"/>
-      <c r="B32" s="85" t="s">
-        <v>279</v>
-      </c>
-      <c r="C32" s="40" t="s">
-        <v>44</v>
-      </c>
-      <c r="D32" s="46" t="s">
-        <v>318</v>
-      </c>
+      <c r="A32" s="82"/>
+      <c r="B32" s="88"/>
+      <c r="C32" s="40"/>
+      <c r="D32" s="40"/>
       <c r="E32" s="40"/>
       <c r="F32" s="40"/>
       <c r="G32" s="40" t="s">
         <v>62</v>
       </c>
       <c r="H32" s="40" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="I32" s="40" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="J32" s="47"/>
     </row>
     <row r="33" spans="1:10" s="42" customFormat="1">
-      <c r="A33" s="91"/>
-      <c r="B33" s="86"/>
+      <c r="A33" s="83"/>
+      <c r="B33" s="89"/>
       <c r="C33" s="40"/>
       <c r="D33" s="40"/>
       <c r="E33" s="40"/>
@@ -3643,62 +3640,62 @@
         <v>62</v>
       </c>
       <c r="H33" s="40" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="I33" s="40" t="s">
+        <v>278</v>
+      </c>
+      <c r="J33" s="47"/>
+    </row>
+    <row r="34" spans="1:10">
+      <c r="A34" s="81" t="s">
+        <v>329</v>
+      </c>
+      <c r="B34" s="84" t="s">
         <v>281</v>
       </c>
-      <c r="J33" s="47"/>
-    </row>
-    <row r="34" spans="1:10" s="42" customFormat="1">
-      <c r="A34" s="92"/>
-      <c r="B34" s="87"/>
-      <c r="C34" s="40"/>
-      <c r="D34" s="40"/>
-      <c r="E34" s="40"/>
-      <c r="F34" s="40"/>
-      <c r="G34" s="40" t="s">
+      <c r="C34" s="35" t="s">
+        <v>279</v>
+      </c>
+      <c r="D34" s="39" t="s">
+        <v>314</v>
+      </c>
+      <c r="E34" s="35" t="s">
+        <v>282</v>
+      </c>
+      <c r="F34" s="35"/>
+      <c r="G34" s="35" t="s">
         <v>62</v>
       </c>
-      <c r="H34" s="40" t="s">
-        <v>317</v>
-      </c>
-      <c r="I34" s="40" t="s">
-        <v>282</v>
-      </c>
-      <c r="J34" s="47"/>
+      <c r="H34" s="35" t="s">
+        <v>313</v>
+      </c>
+      <c r="I34" s="35" t="s">
+        <v>283</v>
+      </c>
+      <c r="J34" s="4"/>
     </row>
     <row r="35" spans="1:10">
-      <c r="A35" s="90" t="s">
-        <v>333</v>
-      </c>
-      <c r="B35" s="82" t="s">
-        <v>285</v>
-      </c>
-      <c r="C35" s="35" t="s">
-        <v>283</v>
-      </c>
-      <c r="D35" s="39" t="s">
-        <v>318</v>
-      </c>
-      <c r="E35" s="35" t="s">
-        <v>286</v>
-      </c>
+      <c r="A35" s="82"/>
+      <c r="B35" s="85"/>
+      <c r="C35" s="35"/>
+      <c r="D35" s="35"/>
+      <c r="E35" s="35"/>
       <c r="F35" s="35"/>
       <c r="G35" s="35" t="s">
         <v>62</v>
       </c>
       <c r="H35" s="35" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="I35" s="35" t="s">
-        <v>287</v>
+        <v>403</v>
       </c>
       <c r="J35" s="4"/>
     </row>
     <row r="36" spans="1:10">
-      <c r="A36" s="91"/>
-      <c r="B36" s="83"/>
+      <c r="A36" s="82"/>
+      <c r="B36" s="85"/>
       <c r="C36" s="35"/>
       <c r="D36" s="35"/>
       <c r="E36" s="35"/>
@@ -3707,16 +3704,16 @@
         <v>62</v>
       </c>
       <c r="H36" s="35" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="I36" s="35" t="s">
-        <v>407</v>
+        <v>39</v>
       </c>
       <c r="J36" s="4"/>
     </row>
     <row r="37" spans="1:10">
-      <c r="A37" s="91"/>
-      <c r="B37" s="83"/>
+      <c r="A37" s="82"/>
+      <c r="B37" s="85"/>
       <c r="C37" s="35"/>
       <c r="D37" s="35"/>
       <c r="E37" s="35"/>
@@ -3725,16 +3722,16 @@
         <v>62</v>
       </c>
       <c r="H37" s="35" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="I37" s="35" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J37" s="4"/>
     </row>
     <row r="38" spans="1:10">
-      <c r="A38" s="91"/>
-      <c r="B38" s="83"/>
+      <c r="A38" s="82"/>
+      <c r="B38" s="85"/>
       <c r="C38" s="35"/>
       <c r="D38" s="35"/>
       <c r="E38" s="35"/>
@@ -3743,58 +3740,58 @@
         <v>62</v>
       </c>
       <c r="H38" s="35" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="I38" s="35" t="s">
-        <v>40</v>
+        <v>404</v>
       </c>
       <c r="J38" s="4"/>
     </row>
-    <row r="39" spans="1:10">
-      <c r="A39" s="91"/>
-      <c r="B39" s="83"/>
-      <c r="C39" s="35"/>
-      <c r="D39" s="35"/>
-      <c r="E39" s="35"/>
-      <c r="F39" s="35"/>
-      <c r="G39" s="35" t="s">
+    <row r="39" spans="1:10" s="42" customFormat="1">
+      <c r="A39" s="82"/>
+      <c r="B39" s="87" t="s">
+        <v>284</v>
+      </c>
+      <c r="C39" s="40" t="s">
+        <v>285</v>
+      </c>
+      <c r="D39" s="46" t="s">
+        <v>314</v>
+      </c>
+      <c r="E39" s="40"/>
+      <c r="F39" s="40"/>
+      <c r="G39" s="40" t="s">
         <v>62</v>
       </c>
-      <c r="H39" s="35" t="s">
-        <v>317</v>
-      </c>
-      <c r="I39" s="35" t="s">
-        <v>408</v>
-      </c>
-      <c r="J39" s="4"/>
+      <c r="H39" s="40" t="s">
+        <v>313</v>
+      </c>
+      <c r="I39" s="40" t="s">
+        <v>405</v>
+      </c>
+      <c r="J39" s="47"/>
     </row>
     <row r="40" spans="1:10" s="42" customFormat="1">
-      <c r="A40" s="91"/>
-      <c r="B40" s="85" t="s">
-        <v>288</v>
-      </c>
-      <c r="C40" s="40" t="s">
-        <v>289</v>
-      </c>
-      <c r="D40" s="46" t="s">
-        <v>318</v>
-      </c>
+      <c r="A40" s="82"/>
+      <c r="B40" s="88"/>
+      <c r="C40" s="40"/>
+      <c r="D40" s="40"/>
       <c r="E40" s="40"/>
       <c r="F40" s="40"/>
       <c r="G40" s="40" t="s">
         <v>62</v>
       </c>
       <c r="H40" s="40" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="I40" s="40" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="J40" s="47"/>
     </row>
     <row r="41" spans="1:10" s="42" customFormat="1">
-      <c r="A41" s="91"/>
-      <c r="B41" s="86"/>
+      <c r="A41" s="82"/>
+      <c r="B41" s="88"/>
       <c r="C41" s="40"/>
       <c r="D41" s="40"/>
       <c r="E41" s="40"/>
@@ -3803,16 +3800,16 @@
         <v>62</v>
       </c>
       <c r="H41" s="40" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="I41" s="40" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="J41" s="47"/>
     </row>
     <row r="42" spans="1:10" s="42" customFormat="1">
-      <c r="A42" s="91"/>
-      <c r="B42" s="86"/>
+      <c r="A42" s="82"/>
+      <c r="B42" s="89"/>
       <c r="C42" s="40"/>
       <c r="D42" s="40"/>
       <c r="E42" s="40"/>
@@ -3821,58 +3818,58 @@
         <v>62</v>
       </c>
       <c r="H42" s="40" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="I42" s="40" t="s">
-        <v>411</v>
+        <v>286</v>
       </c>
       <c r="J42" s="47"/>
     </row>
-    <row r="43" spans="1:10" s="42" customFormat="1">
-      <c r="A43" s="91"/>
-      <c r="B43" s="87"/>
-      <c r="C43" s="40"/>
-      <c r="D43" s="40"/>
-      <c r="E43" s="40"/>
-      <c r="F43" s="40"/>
-      <c r="G43" s="40" t="s">
+    <row r="43" spans="1:10">
+      <c r="A43" s="82"/>
+      <c r="B43" s="84" t="s">
+        <v>333</v>
+      </c>
+      <c r="C43" s="35" t="s">
+        <v>287</v>
+      </c>
+      <c r="D43" s="39" t="s">
+        <v>314</v>
+      </c>
+      <c r="E43" s="35"/>
+      <c r="F43" s="35"/>
+      <c r="G43" s="35" t="s">
         <v>62</v>
       </c>
-      <c r="H43" s="40" t="s">
-        <v>317</v>
-      </c>
-      <c r="I43" s="40" t="s">
-        <v>290</v>
-      </c>
-      <c r="J43" s="47"/>
+      <c r="H43" s="35" t="s">
+        <v>313</v>
+      </c>
+      <c r="I43" s="35" t="s">
+        <v>408</v>
+      </c>
+      <c r="J43" s="4"/>
     </row>
     <row r="44" spans="1:10">
-      <c r="A44" s="91"/>
-      <c r="B44" s="82" t="s">
-        <v>337</v>
-      </c>
-      <c r="C44" s="35" t="s">
-        <v>291</v>
-      </c>
-      <c r="D44" s="39" t="s">
-        <v>318</v>
-      </c>
+      <c r="A44" s="82"/>
+      <c r="B44" s="85"/>
+      <c r="C44" s="35"/>
+      <c r="D44" s="35"/>
       <c r="E44" s="35"/>
       <c r="F44" s="35"/>
       <c r="G44" s="35" t="s">
         <v>62</v>
       </c>
       <c r="H44" s="35" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="I44" s="35" t="s">
-        <v>412</v>
+        <v>657</v>
       </c>
       <c r="J44" s="4"/>
     </row>
     <row r="45" spans="1:10">
-      <c r="A45" s="91"/>
-      <c r="B45" s="83"/>
+      <c r="A45" s="82"/>
+      <c r="B45" s="86"/>
       <c r="C45" s="35"/>
       <c r="D45" s="35"/>
       <c r="E45" s="35"/>
@@ -3881,58 +3878,58 @@
         <v>62</v>
       </c>
       <c r="H45" s="35" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="I45" s="35" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="J45" s="4"/>
     </row>
-    <row r="46" spans="1:10">
-      <c r="A46" s="91"/>
-      <c r="B46" s="84"/>
-      <c r="C46" s="35"/>
-      <c r="D46" s="35"/>
-      <c r="E46" s="35"/>
-      <c r="F46" s="35"/>
-      <c r="G46" s="35" t="s">
+    <row r="46" spans="1:10" s="42" customFormat="1">
+      <c r="A46" s="82"/>
+      <c r="B46" s="87" t="s">
+        <v>332</v>
+      </c>
+      <c r="C46" s="40" t="s">
+        <v>288</v>
+      </c>
+      <c r="D46" s="46" t="s">
+        <v>314</v>
+      </c>
+      <c r="E46" s="40"/>
+      <c r="F46" s="40"/>
+      <c r="G46" s="40" t="s">
         <v>62</v>
       </c>
-      <c r="H46" s="35" t="s">
-        <v>317</v>
-      </c>
-      <c r="I46" s="35" t="s">
-        <v>414</v>
-      </c>
-      <c r="J46" s="4"/>
+      <c r="H46" s="40" t="s">
+        <v>313</v>
+      </c>
+      <c r="I46" s="40" t="s">
+        <v>289</v>
+      </c>
+      <c r="J46" s="47"/>
     </row>
     <row r="47" spans="1:10" s="42" customFormat="1">
-      <c r="A47" s="91"/>
-      <c r="B47" s="85" t="s">
-        <v>336</v>
-      </c>
-      <c r="C47" s="40" t="s">
-        <v>292</v>
-      </c>
-      <c r="D47" s="46" t="s">
-        <v>318</v>
-      </c>
+      <c r="A47" s="82"/>
+      <c r="B47" s="88"/>
+      <c r="C47" s="40"/>
+      <c r="D47" s="40"/>
       <c r="E47" s="40"/>
       <c r="F47" s="40"/>
       <c r="G47" s="40" t="s">
         <v>62</v>
       </c>
       <c r="H47" s="40" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="I47" s="40" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="J47" s="47"/>
     </row>
     <row r="48" spans="1:10" s="42" customFormat="1">
-      <c r="A48" s="91"/>
-      <c r="B48" s="86"/>
+      <c r="A48" s="82"/>
+      <c r="B48" s="88"/>
       <c r="C48" s="40"/>
       <c r="D48" s="40"/>
       <c r="E48" s="40"/>
@@ -3941,16 +3938,15 @@
         <v>62</v>
       </c>
       <c r="H48" s="40" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="I48" s="40" t="s">
-        <v>294</v>
-      </c>
-      <c r="J48" s="47"/>
+        <v>291</v>
+      </c>
     </row>
     <row r="49" spans="1:9" s="42" customFormat="1">
-      <c r="A49" s="91"/>
-      <c r="B49" s="86"/>
+      <c r="A49" s="82"/>
+      <c r="B49" s="88"/>
       <c r="C49" s="40"/>
       <c r="D49" s="40"/>
       <c r="E49" s="40"/>
@@ -3959,15 +3955,15 @@
         <v>62</v>
       </c>
       <c r="H49" s="40" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="I49" s="40" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
     </row>
     <row r="50" spans="1:9" s="42" customFormat="1">
-      <c r="A50" s="91"/>
-      <c r="B50" s="86"/>
+      <c r="A50" s="83"/>
+      <c r="B50" s="89"/>
       <c r="C50" s="40"/>
       <c r="D50" s="40"/>
       <c r="E50" s="40"/>
@@ -3976,57 +3972,57 @@
         <v>62</v>
       </c>
       <c r="H50" s="40" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="I50" s="40" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9" s="42" customFormat="1">
-      <c r="A51" s="92"/>
-      <c r="B51" s="87"/>
-      <c r="C51" s="40"/>
-      <c r="D51" s="40"/>
-      <c r="E51" s="40"/>
-      <c r="F51" s="40"/>
-      <c r="G51" s="40" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9">
+      <c r="A51" s="81" t="s">
+        <v>331</v>
+      </c>
+      <c r="B51" s="84" t="s">
+        <v>304</v>
+      </c>
+      <c r="C51" s="33" t="s">
+        <v>294</v>
+      </c>
+      <c r="D51" s="39" t="s">
+        <v>125</v>
+      </c>
+      <c r="E51" s="33"/>
+      <c r="F51" s="33"/>
+      <c r="G51" s="33" t="s">
         <v>62</v>
       </c>
-      <c r="H51" s="40" t="s">
-        <v>317</v>
-      </c>
-      <c r="I51" s="40" t="s">
-        <v>297</v>
+      <c r="H51" s="35" t="s">
+        <v>313</v>
+      </c>
+      <c r="I51" s="33" t="s">
+        <v>295</v>
       </c>
     </row>
     <row r="52" spans="1:9">
-      <c r="A52" s="90" t="s">
-        <v>335</v>
-      </c>
-      <c r="B52" s="82" t="s">
-        <v>308</v>
-      </c>
-      <c r="C52" s="33" t="s">
-        <v>298</v>
-      </c>
-      <c r="D52" s="39" t="s">
-        <v>125</v>
-      </c>
+      <c r="A52" s="82"/>
+      <c r="B52" s="85"/>
+      <c r="C52" s="33"/>
+      <c r="D52" s="33"/>
       <c r="E52" s="33"/>
       <c r="F52" s="33"/>
       <c r="G52" s="33" t="s">
         <v>62</v>
       </c>
       <c r="H52" s="35" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="I52" s="33" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
     </row>
     <row r="53" spans="1:9">
-      <c r="A53" s="91"/>
-      <c r="B53" s="83"/>
+      <c r="A53" s="82"/>
+      <c r="B53" s="85"/>
       <c r="C53" s="33"/>
       <c r="D53" s="33"/>
       <c r="E53" s="33"/>
@@ -4035,15 +4031,15 @@
         <v>62</v>
       </c>
       <c r="H53" s="35" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="I53" s="33" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
     </row>
     <row r="54" spans="1:9">
-      <c r="A54" s="91"/>
-      <c r="B54" s="83"/>
+      <c r="A54" s="82"/>
+      <c r="B54" s="86"/>
       <c r="C54" s="33"/>
       <c r="D54" s="33"/>
       <c r="E54" s="33"/>
@@ -4052,55 +4048,55 @@
         <v>62</v>
       </c>
       <c r="H54" s="35" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="I54" s="33" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9">
-      <c r="A55" s="91"/>
-      <c r="B55" s="84"/>
-      <c r="C55" s="33"/>
-      <c r="D55" s="33"/>
-      <c r="E55" s="33"/>
-      <c r="F55" s="33"/>
-      <c r="G55" s="33" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" s="42" customFormat="1">
+      <c r="A55" s="82"/>
+      <c r="B55" s="87" t="s">
+        <v>305</v>
+      </c>
+      <c r="C55" s="43" t="s">
+        <v>306</v>
+      </c>
+      <c r="D55" s="46" t="s">
+        <v>315</v>
+      </c>
+      <c r="E55" s="43"/>
+      <c r="F55" s="43"/>
+      <c r="G55" s="43" t="s">
         <v>62</v>
       </c>
-      <c r="H55" s="35" t="s">
-        <v>317</v>
-      </c>
-      <c r="I55" s="33" t="s">
-        <v>302</v>
+      <c r="H55" s="40" t="s">
+        <v>313</v>
+      </c>
+      <c r="I55" s="43" t="s">
+        <v>307</v>
       </c>
     </row>
     <row r="56" spans="1:9" s="42" customFormat="1">
-      <c r="A56" s="91"/>
-      <c r="B56" s="85" t="s">
-        <v>309</v>
-      </c>
-      <c r="C56" s="43" t="s">
-        <v>310</v>
-      </c>
-      <c r="D56" s="46" t="s">
-        <v>319</v>
-      </c>
+      <c r="A56" s="82"/>
+      <c r="B56" s="88"/>
+      <c r="C56" s="43"/>
+      <c r="D56" s="43"/>
       <c r="E56" s="43"/>
       <c r="F56" s="43"/>
       <c r="G56" s="43" t="s">
         <v>62</v>
       </c>
       <c r="H56" s="40" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="I56" s="43" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
     </row>
     <row r="57" spans="1:9" s="42" customFormat="1">
-      <c r="A57" s="91"/>
-      <c r="B57" s="86"/>
+      <c r="A57" s="82"/>
+      <c r="B57" s="88"/>
       <c r="C57" s="43"/>
       <c r="D57" s="43"/>
       <c r="E57" s="43"/>
@@ -4109,15 +4105,15 @@
         <v>62</v>
       </c>
       <c r="H57" s="40" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="I57" s="43" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
     </row>
     <row r="58" spans="1:9" s="42" customFormat="1">
-      <c r="A58" s="91"/>
-      <c r="B58" s="86"/>
+      <c r="A58" s="82"/>
+      <c r="B58" s="89"/>
       <c r="C58" s="43"/>
       <c r="D58" s="43"/>
       <c r="E58" s="43"/>
@@ -4126,224 +4122,193 @@
         <v>62</v>
       </c>
       <c r="H58" s="40" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="I58" s="43" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9" s="42" customFormat="1">
-      <c r="A59" s="91"/>
-      <c r="B59" s="87"/>
-      <c r="C59" s="43"/>
-      <c r="D59" s="43"/>
-      <c r="E59" s="43"/>
-      <c r="F59" s="43"/>
-      <c r="G59" s="43" t="s">
-        <v>62</v>
-      </c>
-      <c r="H59" s="40" t="s">
-        <v>317</v>
-      </c>
-      <c r="I59" s="43" t="s">
-        <v>314</v>
+        <v>310</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9">
+      <c r="A59" s="82"/>
+      <c r="B59" s="84" t="s">
+        <v>311</v>
+      </c>
+      <c r="C59" s="33"/>
+      <c r="D59" s="39" t="s">
+        <v>315</v>
+      </c>
+      <c r="E59" s="33"/>
+      <c r="F59" s="33"/>
+      <c r="G59" s="33"/>
+      <c r="H59" s="35" t="s">
+        <v>392</v>
+      </c>
+      <c r="I59" s="33" t="s">
+        <v>318</v>
       </c>
     </row>
     <row r="60" spans="1:9">
-      <c r="A60" s="91"/>
-      <c r="B60" s="82" t="s">
-        <v>315</v>
-      </c>
+      <c r="A60" s="82"/>
+      <c r="B60" s="85"/>
       <c r="C60" s="33"/>
-      <c r="D60" s="39" t="s">
-        <v>319</v>
-      </c>
-      <c r="E60" s="33"/>
       <c r="F60" s="33"/>
       <c r="G60" s="33"/>
-      <c r="H60" s="35" t="s">
-        <v>396</v>
-      </c>
-      <c r="I60" s="33" t="s">
-        <v>322</v>
+      <c r="H60" s="33" t="s">
+        <v>393</v>
+      </c>
+      <c r="I60" s="35" t="s">
+        <v>312</v>
       </c>
     </row>
     <row r="61" spans="1:9">
-      <c r="A61" s="91"/>
-      <c r="B61" s="83"/>
+      <c r="A61" s="82"/>
+      <c r="B61" s="85"/>
       <c r="C61" s="33"/>
+      <c r="D61" s="33"/>
       <c r="F61" s="33"/>
       <c r="G61" s="33"/>
       <c r="H61" s="33" t="s">
-        <v>397</v>
-      </c>
-      <c r="I61" s="35" t="s">
+        <v>393</v>
+      </c>
+      <c r="I61" s="33" t="s">
         <v>316</v>
       </c>
     </row>
     <row r="62" spans="1:9">
-      <c r="A62" s="91"/>
-      <c r="B62" s="83"/>
+      <c r="A62" s="82"/>
+      <c r="B62" s="86"/>
       <c r="C62" s="33"/>
       <c r="D62" s="33"/>
       <c r="F62" s="33"/>
       <c r="G62" s="33"/>
       <c r="H62" s="33" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="I62" s="33" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="63" spans="1:9">
-      <c r="A63" s="91"/>
-      <c r="B63" s="84"/>
-      <c r="C63" s="33"/>
-      <c r="D63" s="33"/>
-      <c r="F63" s="33"/>
-      <c r="G63" s="33"/>
-      <c r="H63" s="33" t="s">
-        <v>397</v>
-      </c>
-      <c r="I63" s="33" t="s">
-        <v>321</v>
+        <v>317</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" s="42" customFormat="1">
+      <c r="A63" s="82"/>
+      <c r="B63" s="87" t="s">
+        <v>299</v>
+      </c>
+      <c r="C63" s="43" t="s">
+        <v>300</v>
+      </c>
+      <c r="D63" s="46" t="s">
+        <v>314</v>
+      </c>
+      <c r="E63" s="43"/>
+      <c r="F63" s="43"/>
+      <c r="G63" s="43" t="s">
+        <v>62</v>
+      </c>
+      <c r="H63" s="64" t="s">
+        <v>264</v>
+      </c>
+      <c r="I63" s="43" t="s">
+        <v>410</v>
       </c>
     </row>
     <row r="64" spans="1:9" s="42" customFormat="1">
-      <c r="A64" s="91"/>
-      <c r="B64" s="85" t="s">
-        <v>303</v>
-      </c>
-      <c r="C64" s="43" t="s">
-        <v>304</v>
-      </c>
-      <c r="D64" s="46" t="s">
-        <v>318</v>
-      </c>
+      <c r="A64" s="82"/>
+      <c r="B64" s="88"/>
+      <c r="C64" s="43"/>
+      <c r="D64" s="43"/>
       <c r="E64" s="43"/>
       <c r="F64" s="43"/>
-      <c r="G64" s="43" t="s">
-        <v>62</v>
-      </c>
+      <c r="G64" s="43"/>
       <c r="H64" s="64" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="I64" s="43" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
     </row>
     <row r="65" spans="1:9" s="42" customFormat="1">
-      <c r="A65" s="91"/>
-      <c r="B65" s="86"/>
+      <c r="A65" s="83"/>
+      <c r="B65" s="89"/>
       <c r="C65" s="43"/>
       <c r="D65" s="43"/>
       <c r="E65" s="43"/>
       <c r="F65" s="43"/>
       <c r="G65" s="43"/>
       <c r="H65" s="64" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="I65" s="43" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="66" spans="1:9" s="42" customFormat="1">
-      <c r="A66" s="92"/>
-      <c r="B66" s="87"/>
-      <c r="C66" s="43"/>
-      <c r="D66" s="43"/>
-      <c r="E66" s="43"/>
-      <c r="F66" s="43"/>
-      <c r="G66" s="43"/>
-      <c r="H66" s="64" t="s">
-        <v>266</v>
-      </c>
-      <c r="I66" s="43" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="67" spans="1:9" s="57" customFormat="1" ht="17" thickBot="1">
-      <c r="A67" s="58" t="s">
-        <v>334</v>
-      </c>
-      <c r="B67" s="53" t="s">
-        <v>305</v>
-      </c>
-      <c r="C67" s="53" t="s">
-        <v>306</v>
-      </c>
-      <c r="D67" s="54" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" s="57" customFormat="1" ht="17" thickBot="1">
+      <c r="A66" s="58" t="s">
+        <v>330</v>
+      </c>
+      <c r="B66" s="53" t="s">
+        <v>301</v>
+      </c>
+      <c r="C66" s="53" t="s">
+        <v>302</v>
+      </c>
+      <c r="D66" s="54" t="s">
         <v>125</v>
       </c>
-      <c r="E67" s="55"/>
-      <c r="F67" s="55"/>
-      <c r="G67" s="56" t="s">
-        <v>254</v>
-      </c>
-      <c r="H67" s="56"/>
-      <c r="I67" s="56"/>
+      <c r="E66" s="55"/>
+      <c r="F66" s="55"/>
+      <c r="G66" s="56" t="s">
+        <v>252</v>
+      </c>
+      <c r="H66" s="56"/>
+      <c r="I66" s="56"/>
+    </row>
+    <row r="67" spans="1:9">
+      <c r="A67" s="59"/>
+      <c r="B67" s="49"/>
+      <c r="C67" s="49"/>
+      <c r="D67" s="50"/>
+      <c r="E67" s="51"/>
+      <c r="F67" s="51"/>
+      <c r="G67" s="52"/>
+      <c r="H67" s="52"/>
+      <c r="I67" s="52"/>
     </row>
     <row r="68" spans="1:9">
-      <c r="A68" s="59"/>
-      <c r="B68" s="49"/>
-      <c r="C68" s="49"/>
-      <c r="D68" s="50"/>
-      <c r="E68" s="51"/>
-      <c r="F68" s="51"/>
-      <c r="G68" s="52"/>
-      <c r="H68" s="52"/>
-      <c r="I68" s="52"/>
+      <c r="A68" s="60"/>
+      <c r="B68" s="33" t="s">
+        <v>255</v>
+      </c>
     </row>
     <row r="69" spans="1:9">
       <c r="A69" s="60"/>
       <c r="B69" s="33" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="70" spans="1:9">
       <c r="A70" s="60"/>
       <c r="B70" s="33" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="71" spans="1:9">
       <c r="A71" s="60"/>
       <c r="B71" s="33" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="72" spans="1:9">
-      <c r="A72" s="60"/>
       <c r="B72" s="33" t="s">
-        <v>260</v>
+        <v>267</v>
       </c>
     </row>
     <row r="73" spans="1:9">
       <c r="B73" s="33" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="74" spans="1:9">
-      <c r="B74" s="33" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="A52:A66"/>
-    <mergeCell ref="B52:B55"/>
-    <mergeCell ref="B56:B59"/>
-    <mergeCell ref="B60:B63"/>
-    <mergeCell ref="B64:B66"/>
-    <mergeCell ref="B21:B23"/>
-    <mergeCell ref="B28:B31"/>
-    <mergeCell ref="A21:A34"/>
-    <mergeCell ref="A35:A51"/>
-    <mergeCell ref="B32:B34"/>
-    <mergeCell ref="B35:B39"/>
-    <mergeCell ref="B40:B43"/>
-    <mergeCell ref="B44:B46"/>
-    <mergeCell ref="B47:B51"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="B9:B11"/>
     <mergeCell ref="B12:B14"/>
@@ -4352,6 +4317,20 @@
     <mergeCell ref="A9:A20"/>
     <mergeCell ref="B15:B17"/>
     <mergeCell ref="B18:B20"/>
+    <mergeCell ref="B21:B23"/>
+    <mergeCell ref="B28:B30"/>
+    <mergeCell ref="A21:A33"/>
+    <mergeCell ref="A34:A50"/>
+    <mergeCell ref="B31:B33"/>
+    <mergeCell ref="B34:B38"/>
+    <mergeCell ref="B39:B42"/>
+    <mergeCell ref="B43:B45"/>
+    <mergeCell ref="B46:B50"/>
+    <mergeCell ref="A51:A65"/>
+    <mergeCell ref="B51:B54"/>
+    <mergeCell ref="B55:B58"/>
+    <mergeCell ref="B59:B62"/>
+    <mergeCell ref="B63:B65"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="33" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -4379,7 +4358,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="34.5" customHeight="1" thickBot="1">
       <c r="A1" s="93" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="B1" s="93"/>
       <c r="C1" s="93"/>
@@ -4392,7 +4371,7 @@
     </row>
     <row r="2" spans="1:9" ht="17" thickBot="1">
       <c r="A2" s="16" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="B2" s="16" t="s">
         <v>0</v>
@@ -4421,7 +4400,7 @@
     </row>
     <row r="3" spans="1:9" ht="32">
       <c r="A3" s="12" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="B3" s="21" t="s">
         <v>52</v>
@@ -4435,13 +4414,13 @@
       <c r="E3" s="4"/>
       <c r="F3" s="6"/>
       <c r="G3" s="6" t="s">
-        <v>637</v>
+        <v>632</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>648</v>
+        <v>642</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>638</v>
+        <v>633</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="32">
@@ -4450,7 +4429,7 @@
         <v>52</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>60</v>
@@ -4458,13 +4437,13 @@
       <c r="E4" s="4"/>
       <c r="F4" s="6"/>
       <c r="G4" s="6" t="s">
-        <v>637</v>
+        <v>632</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>648</v>
+        <v>642</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>639</v>
+        <v>634</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="32">
@@ -4473,7 +4452,7 @@
         <v>52</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>60</v>
@@ -4481,22 +4460,22 @@
       <c r="E5" s="4"/>
       <c r="F5" s="6"/>
       <c r="G5" s="6" t="s">
-        <v>637</v>
+        <v>632</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>648</v>
+        <v>642</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>640</v>
+        <v>635</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="8"/>
       <c r="B6" s="4" t="s">
-        <v>641</v>
+        <v>636</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>60</v>
@@ -4504,10 +4483,10 @@
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
       <c r="G6" s="6" t="s">
-        <v>637</v>
+        <v>632</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>649</v>
+        <v>643</v>
       </c>
       <c r="I6" s="4" t="s">
         <v>169</v>
@@ -4516,10 +4495,10 @@
     <row r="7" spans="1:9">
       <c r="A7" s="8"/>
       <c r="B7" s="4" t="s">
-        <v>642</v>
+        <v>637</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>60</v>
@@ -4527,22 +4506,22 @@
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
       <c r="G7" s="6" t="s">
-        <v>637</v>
+        <v>632</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>649</v>
+        <v>643</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>643</v>
+        <v>638</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="8"/>
       <c r="B8" s="4" t="s">
-        <v>644</v>
+        <v>639</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>60</v>
@@ -4550,10 +4529,10 @@
       <c r="E8" s="4"/>
       <c r="F8" s="4"/>
       <c r="G8" s="6" t="s">
-        <v>637</v>
+        <v>632</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>650</v>
+        <v>644</v>
       </c>
       <c r="I8" s="4" t="s">
         <v>170</v>
@@ -4562,10 +4541,10 @@
     <row r="9" spans="1:9">
       <c r="A9" s="8"/>
       <c r="B9" s="4" t="s">
-        <v>645</v>
+        <v>640</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>60</v>
@@ -4573,13 +4552,13 @@
       <c r="E9" s="4"/>
       <c r="F9" s="4"/>
       <c r="G9" s="6" t="s">
-        <v>637</v>
+        <v>632</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>650</v>
+        <v>644</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>646</v>
+        <v>641</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -4590,13 +4569,13 @@
         <v>185</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>125</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>187</v>
@@ -4605,7 +4584,7 @@
         <v>62</v>
       </c>
       <c r="H10" s="75" t="s">
-        <v>632</v>
+        <v>627</v>
       </c>
       <c r="I10" s="4" t="s">
         <v>18</v>
@@ -4622,7 +4601,7 @@
       </c>
       <c r="G11" s="4"/>
       <c r="H11" s="75" t="s">
-        <v>632</v>
+        <v>627</v>
       </c>
       <c r="I11" s="4" t="s">
         <v>19</v>
@@ -4639,7 +4618,7 @@
       </c>
       <c r="G12" s="4"/>
       <c r="H12" s="75" t="s">
-        <v>632</v>
+        <v>627</v>
       </c>
       <c r="I12" s="4" t="s">
         <v>20</v>
@@ -4656,7 +4635,7 @@
       </c>
       <c r="G13" s="4"/>
       <c r="H13" s="75" t="s">
-        <v>632</v>
+        <v>627</v>
       </c>
       <c r="I13" s="4" t="s">
         <v>21</v>
@@ -4673,7 +4652,7 @@
       </c>
       <c r="G14" s="4"/>
       <c r="H14" s="75" t="s">
-        <v>632</v>
+        <v>627</v>
       </c>
       <c r="I14" s="4" t="s">
         <v>22</v>
@@ -4690,7 +4669,7 @@
       </c>
       <c r="G15" s="4"/>
       <c r="H15" s="75" t="s">
-        <v>632</v>
+        <v>627</v>
       </c>
       <c r="I15" s="4" t="s">
         <v>23</v>
@@ -4707,7 +4686,7 @@
       </c>
       <c r="G16" s="4"/>
       <c r="H16" s="75" t="s">
-        <v>632</v>
+        <v>627</v>
       </c>
       <c r="I16" s="4" t="s">
         <v>24</v>
@@ -4724,7 +4703,7 @@
       </c>
       <c r="G17" s="4"/>
       <c r="H17" s="75" t="s">
-        <v>632</v>
+        <v>627</v>
       </c>
       <c r="I17" s="4" t="s">
         <v>25</v>
@@ -4741,7 +4720,7 @@
       </c>
       <c r="G18" s="4"/>
       <c r="H18" s="75" t="s">
-        <v>632</v>
+        <v>627</v>
       </c>
       <c r="I18" s="4" t="s">
         <v>26</v>
@@ -4758,7 +4737,7 @@
       </c>
       <c r="G19" s="4"/>
       <c r="H19" s="75" t="s">
-        <v>632</v>
+        <v>627</v>
       </c>
       <c r="I19" s="4" t="s">
         <v>27</v>
@@ -4766,10 +4745,10 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="12" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>188</v>
@@ -4778,7 +4757,7 @@
         <v>125</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="F20" s="4" t="s">
         <v>187</v>
@@ -4787,7 +4766,7 @@
         <v>62</v>
       </c>
       <c r="H20" s="75" t="s">
-        <v>633</v>
+        <v>628</v>
       </c>
       <c r="I20" s="4" t="s">
         <v>2</v>
@@ -4805,7 +4784,7 @@
       </c>
       <c r="G21" s="4"/>
       <c r="H21" s="75" t="s">
-        <v>633</v>
+        <v>628</v>
       </c>
       <c r="I21" s="4" t="s">
         <v>3</v>
@@ -4823,7 +4802,7 @@
       </c>
       <c r="G22" s="4"/>
       <c r="H22" s="75" t="s">
-        <v>633</v>
+        <v>628</v>
       </c>
       <c r="I22" s="4" t="s">
         <v>4</v>
@@ -4833,7 +4812,7 @@
     <row r="23" spans="1:10">
       <c r="A23" s="12"/>
       <c r="B23" s="6" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C23" s="6"/>
       <c r="D23" s="4"/>
@@ -4843,7 +4822,7 @@
       </c>
       <c r="G23" s="4"/>
       <c r="H23" s="75" t="s">
-        <v>633</v>
+        <v>628</v>
       </c>
       <c r="I23" s="4" t="s">
         <v>5</v>
@@ -4861,7 +4840,7 @@
       </c>
       <c r="G24" s="4"/>
       <c r="H24" s="75" t="s">
-        <v>633</v>
+        <v>628</v>
       </c>
       <c r="I24" s="4" t="s">
         <v>6</v>
@@ -4879,7 +4858,7 @@
       </c>
       <c r="G25" s="4"/>
       <c r="H25" s="75" t="s">
-        <v>633</v>
+        <v>628</v>
       </c>
       <c r="I25" s="4" t="s">
         <v>7</v>
@@ -4889,7 +4868,7 @@
     <row r="26" spans="1:10">
       <c r="A26" s="6"/>
       <c r="B26" s="6" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="4"/>
@@ -4899,7 +4878,7 @@
       </c>
       <c r="G26" s="4"/>
       <c r="H26" s="75" t="s">
-        <v>633</v>
+        <v>628</v>
       </c>
       <c r="I26" s="4" t="s">
         <v>8</v>
@@ -4917,7 +4896,7 @@
       </c>
       <c r="G27" s="4"/>
       <c r="H27" s="75" t="s">
-        <v>633</v>
+        <v>628</v>
       </c>
       <c r="I27" s="4" t="s">
         <v>9</v>
@@ -4935,7 +4914,7 @@
       </c>
       <c r="G28" s="4"/>
       <c r="H28" s="75" t="s">
-        <v>633</v>
+        <v>628</v>
       </c>
       <c r="I28" s="4" t="s">
         <v>10</v>
@@ -4945,7 +4924,7 @@
     <row r="29" spans="1:10">
       <c r="A29" s="6"/>
       <c r="B29" s="6" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C29" s="6"/>
       <c r="D29" s="4"/>
@@ -4955,7 +4934,7 @@
       </c>
       <c r="G29" s="4"/>
       <c r="H29" s="75" t="s">
-        <v>633</v>
+        <v>628</v>
       </c>
       <c r="I29" s="4" t="s">
         <v>11</v>
@@ -4997,7 +4976,7 @@
     <row r="32" spans="1:10">
       <c r="A32" s="6"/>
       <c r="B32" s="6" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="4"/>
@@ -5062,19 +5041,19 @@
     </row>
     <row r="36" spans="1:10">
       <c r="A36" s="12" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D36" s="6" t="s">
         <v>60</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="F36" s="4" t="s">
         <v>121</v>
@@ -5083,7 +5062,7 @@
         <v>62</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>199</v>
+        <v>653</v>
       </c>
       <c r="I36" s="4" t="s">
         <v>191</v>
@@ -5098,7 +5077,7 @@
       <c r="F37" s="4"/>
       <c r="G37" s="4"/>
       <c r="H37" s="4" t="s">
-        <v>199</v>
+        <v>653</v>
       </c>
       <c r="I37" s="4" t="s">
         <v>192</v>
@@ -5113,7 +5092,7 @@
       <c r="F38" s="4"/>
       <c r="G38" s="4"/>
       <c r="H38" s="4" t="s">
-        <v>199</v>
+        <v>653</v>
       </c>
       <c r="I38" s="4" t="s">
         <v>193</v>
@@ -5128,7 +5107,7 @@
       <c r="F39" s="4"/>
       <c r="G39" s="4"/>
       <c r="H39" s="4" t="s">
-        <v>199</v>
+        <v>653</v>
       </c>
       <c r="I39" s="4" t="s">
         <v>194</v>
@@ -5143,7 +5122,7 @@
       <c r="F40" s="4"/>
       <c r="G40" s="4"/>
       <c r="H40" s="4" t="s">
-        <v>199</v>
+        <v>653</v>
       </c>
       <c r="I40" s="4" t="s">
         <v>195</v>
@@ -5158,7 +5137,7 @@
       <c r="F41" s="4"/>
       <c r="G41" s="4"/>
       <c r="H41" s="4" t="s">
-        <v>199</v>
+        <v>653</v>
       </c>
       <c r="I41" s="4" t="s">
         <v>196</v>
@@ -5173,7 +5152,7 @@
       <c r="F42" s="4"/>
       <c r="G42" s="4"/>
       <c r="H42" s="4" t="s">
-        <v>199</v>
+        <v>653</v>
       </c>
       <c r="I42" s="4" t="s">
         <v>197</v>
@@ -5190,7 +5169,7 @@
       <c r="F43" s="4"/>
       <c r="G43" s="4"/>
       <c r="H43" s="4" t="s">
-        <v>200</v>
+        <v>654</v>
       </c>
       <c r="I43" s="4" t="s">
         <v>198</v>
@@ -5199,7 +5178,7 @@
     <row r="44" spans="1:10">
       <c r="A44" s="6"/>
       <c r="B44" s="6" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C44" s="6" t="s">
         <v>65</v>
@@ -5208,17 +5187,17 @@
         <v>60</v>
       </c>
       <c r="E44" s="7" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="F44" s="6"/>
       <c r="G44" s="4" t="s">
         <v>62</v>
       </c>
       <c r="H44" s="73" t="s">
-        <v>631</v>
+        <v>626</v>
       </c>
       <c r="I44" s="4" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="J44" s="4"/>
     </row>
@@ -5231,10 +5210,10 @@
       <c r="F45" s="4"/>
       <c r="G45" s="4"/>
       <c r="H45" s="73" t="s">
-        <v>631</v>
+        <v>626</v>
       </c>
       <c r="I45" s="4" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="J45" s="4"/>
     </row>
@@ -5247,10 +5226,10 @@
       <c r="F46" s="4"/>
       <c r="G46" s="4"/>
       <c r="H46" s="73" t="s">
-        <v>631</v>
+        <v>626</v>
       </c>
       <c r="I46" s="4" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="J46" s="4"/>
     </row>
@@ -5263,10 +5242,10 @@
       <c r="F47" s="4"/>
       <c r="G47" s="4"/>
       <c r="H47" s="73" t="s">
-        <v>631</v>
+        <v>626</v>
       </c>
       <c r="I47" s="4" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="J47" s="4"/>
     </row>
@@ -5279,10 +5258,10 @@
       <c r="F48" s="4"/>
       <c r="G48" s="4"/>
       <c r="H48" s="73" t="s">
-        <v>631</v>
+        <v>626</v>
       </c>
       <c r="I48" s="4" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="J48" s="4"/>
     </row>
@@ -5295,36 +5274,36 @@
       <c r="F49" s="4"/>
       <c r="G49" s="4"/>
       <c r="H49" s="73" t="s">
-        <v>631</v>
+        <v>626</v>
       </c>
       <c r="I49" s="4" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="J49" s="4"/>
     </row>
     <row r="50" spans="1:10">
       <c r="A50" s="6"/>
       <c r="B50" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="C50" s="6" t="s">
         <v>240</v>
-      </c>
-      <c r="C50" s="6" t="s">
-        <v>242</v>
       </c>
       <c r="D50" s="6" t="s">
         <v>60</v>
       </c>
       <c r="E50" s="7" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="F50" s="6"/>
       <c r="G50" s="6" t="s">
         <v>62</v>
       </c>
       <c r="H50" s="73" t="s">
-        <v>631</v>
+        <v>626</v>
       </c>
       <c r="I50" s="6" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="J50" s="4"/>
     </row>
@@ -5339,64 +5318,64 @@
         <v>62</v>
       </c>
       <c r="H51" s="73" t="s">
-        <v>631</v>
+        <v>626</v>
       </c>
       <c r="I51" s="6" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="J51" s="4"/>
     </row>
     <row r="52" spans="1:10">
       <c r="A52" s="6"/>
       <c r="B52" s="6" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="D52" s="6" t="s">
         <v>60</v>
       </c>
       <c r="E52" s="4"/>
       <c r="F52" s="6" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="G52" s="6" t="s">
         <v>62</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>634</v>
+        <v>629</v>
       </c>
       <c r="I52" s="6" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="J52" s="4"/>
     </row>
     <row r="53" spans="1:10" s="24" customFormat="1">
       <c r="A53" s="26" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B53" s="13" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C53" s="19" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D53" s="13" t="s">
         <v>60</v>
       </c>
       <c r="E53" s="14" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="F53" s="19"/>
       <c r="G53" s="13" t="s">
         <v>62</v>
       </c>
       <c r="H53" s="19" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="I53" s="66" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="54" spans="1:10">
@@ -5408,10 +5387,10 @@
       <c r="F54" s="5"/>
       <c r="G54" s="5"/>
       <c r="H54" s="5" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="I54" s="67" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="55" spans="1:10">
@@ -5423,10 +5402,10 @@
       <c r="F55" s="5"/>
       <c r="G55" s="5"/>
       <c r="H55" s="5" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="I55" s="67" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="56" spans="1:10">
@@ -5438,16 +5417,16 @@
       <c r="F56" s="5"/>
       <c r="G56" s="5"/>
       <c r="H56" s="5" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="I56" s="67" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="57" spans="1:10">
       <c r="A57" s="5"/>
       <c r="B57" s="6" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C57" s="5"/>
       <c r="D57" s="5"/>
@@ -5457,10 +5436,10 @@
         <v>62</v>
       </c>
       <c r="H57" s="5" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="I57" s="67" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
     </row>
     <row r="58" spans="1:10">
@@ -5472,10 +5451,10 @@
       <c r="F58" s="5"/>
       <c r="G58" s="5"/>
       <c r="H58" s="5" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="I58" s="67" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
     </row>
     <row r="59" spans="1:10">
@@ -5487,10 +5466,10 @@
       <c r="F59" s="5"/>
       <c r="G59" s="5"/>
       <c r="H59" s="5" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="I59" s="67" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
     </row>
     <row r="60" spans="1:10">
@@ -5502,10 +5481,10 @@
       <c r="F60" s="5"/>
       <c r="G60" s="5"/>
       <c r="H60" s="5" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="I60" s="4" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
     </row>
     <row r="61" spans="1:10">
@@ -5517,10 +5496,10 @@
       <c r="F61" s="5"/>
       <c r="G61" s="5"/>
       <c r="H61" s="5" t="s">
+        <v>413</v>
+      </c>
+      <c r="I61" s="4" t="s">
         <v>418</v>
-      </c>
-      <c r="I61" s="4" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="62" spans="1:10">
@@ -5532,16 +5511,16 @@
       <c r="F62" s="5"/>
       <c r="G62" s="5"/>
       <c r="H62" s="5" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="I62" s="4" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
     </row>
     <row r="63" spans="1:10">
       <c r="A63" s="5"/>
       <c r="B63" s="6" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C63" s="5"/>
       <c r="D63" s="5"/>
@@ -5551,10 +5530,10 @@
         <v>62</v>
       </c>
       <c r="H63" s="5" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="I63" s="67" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
     </row>
     <row r="64" spans="1:10">
@@ -5566,10 +5545,10 @@
       <c r="F64" s="5"/>
       <c r="G64" s="5"/>
       <c r="H64" s="5" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="I64" s="4" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
     </row>
     <row r="65" spans="1:10">
@@ -5581,10 +5560,10 @@
       <c r="F65" s="5"/>
       <c r="G65" s="5"/>
       <c r="H65" s="5" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="I65" s="4" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
     </row>
     <row r="66" spans="1:10">
@@ -5596,10 +5575,10 @@
       <c r="F66" s="5"/>
       <c r="G66" s="5"/>
       <c r="H66" s="5" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="I66" s="4" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
     </row>
     <row r="67" spans="1:10">
@@ -5611,16 +5590,16 @@
       <c r="F67" s="5"/>
       <c r="G67" s="5"/>
       <c r="H67" s="5" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="I67" s="4" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
     </row>
     <row r="68" spans="1:10">
       <c r="A68" s="5"/>
       <c r="B68" s="6" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C68" s="5"/>
       <c r="D68" s="5"/>
@@ -5630,10 +5609,10 @@
         <v>62</v>
       </c>
       <c r="H68" s="5" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="I68" s="4" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
     </row>
     <row r="69" spans="1:10">
@@ -5645,10 +5624,10 @@
       <c r="F69" s="5"/>
       <c r="G69" s="5"/>
       <c r="H69" s="5" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="I69" s="4" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="J69" s="6"/>
     </row>
@@ -5661,17 +5640,17 @@
       <c r="F70" s="5"/>
       <c r="G70" s="5"/>
       <c r="H70" s="65" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="I70" s="15" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="J70" s="6"/>
     </row>
     <row r="71" spans="1:10" s="24" customFormat="1">
       <c r="A71" s="19"/>
       <c r="B71" s="19" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C71" s="19" t="s">
         <v>65</v>
@@ -5680,7 +5659,7 @@
         <v>60</v>
       </c>
       <c r="E71" s="19" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="F71" s="19"/>
       <c r="G71" s="19" t="s">
@@ -5690,7 +5669,7 @@
         <v>1</v>
       </c>
       <c r="I71" s="5" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="72" spans="1:10">
@@ -5705,7 +5684,7 @@
         <v>2</v>
       </c>
       <c r="I72" s="5" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="73" spans="1:10">
@@ -5720,7 +5699,7 @@
         <v>3</v>
       </c>
       <c r="I73" s="5" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="74" spans="1:10">
@@ -5735,7 +5714,7 @@
         <v>4</v>
       </c>
       <c r="I74" s="5" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="75" spans="1:10">
@@ -5750,7 +5729,7 @@
         <v>5</v>
       </c>
       <c r="I75" s="5" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="76" spans="1:10">
@@ -5765,7 +5744,7 @@
         <v>6</v>
       </c>
       <c r="I76" s="5" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="77" spans="1:10">
@@ -5780,7 +5759,7 @@
         <v>7</v>
       </c>
       <c r="I77" s="5" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="78" spans="1:10">
@@ -5795,7 +5774,7 @@
         <v>8</v>
       </c>
       <c r="I78" s="5" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="79" spans="1:10">
@@ -5810,15 +5789,15 @@
         <v>9</v>
       </c>
       <c r="I79" s="5" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="80" spans="1:10">
       <c r="A80" s="12" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C80" s="5" t="s">
         <v>65</v>
@@ -5832,10 +5811,10 @@
         <v>62</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>635</v>
+        <v>630</v>
       </c>
       <c r="I80" s="4" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="81" spans="1:9">
@@ -5866,17 +5845,17 @@
     </row>
     <row r="85" spans="1:9">
       <c r="B85" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="86" spans="1:9">
       <c r="B86" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="87" spans="1:9">
       <c r="B87" s="8" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
   </sheetData>
@@ -5913,7 +5892,7 @@
   <sheetData>
     <row r="1" spans="1:11" ht="47.25" customHeight="1" thickBot="1">
       <c r="A1" s="94" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="B1" s="94"/>
       <c r="C1" s="94"/>
@@ -5928,7 +5907,7 @@
     </row>
     <row r="2" spans="1:11" ht="17" thickBot="1">
       <c r="A2" s="16" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="B2" s="16" t="s">
         <v>0</v>
@@ -5958,12 +5937,12 @@
         <v>42</v>
       </c>
       <c r="K2" s="16" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="12" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>51</v>
@@ -5979,7 +5958,7 @@
         <v>118</v>
       </c>
       <c r="H3" s="78" t="s">
-        <v>637</v>
+        <v>632</v>
       </c>
       <c r="I3" s="79" t="s">
         <v>655</v>
@@ -6003,7 +5982,7 @@
         <v>62</v>
       </c>
       <c r="I4" s="77" t="s">
-        <v>651</v>
+        <v>645</v>
       </c>
       <c r="J4" s="77" t="s">
         <v>120</v>
@@ -6012,19 +5991,19 @@
     </row>
     <row r="5" spans="1:11">
       <c r="B5" s="77" t="s">
-        <v>656</v>
+        <v>648</v>
       </c>
       <c r="D5" s="77" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>60</v>
       </c>
       <c r="H5" s="78" t="s">
-        <v>637</v>
+        <v>632</v>
       </c>
       <c r="I5" s="77" t="s">
-        <v>649</v>
+        <v>643</v>
       </c>
       <c r="J5" s="77" t="s">
         <v>169</v>
@@ -6033,19 +6012,19 @@
     </row>
     <row r="6" spans="1:11">
       <c r="B6" s="77" t="s">
-        <v>657</v>
+        <v>649</v>
       </c>
       <c r="D6" s="77" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>60</v>
       </c>
       <c r="H6" s="78" t="s">
-        <v>637</v>
+        <v>632</v>
       </c>
       <c r="I6" s="77" t="s">
-        <v>650</v>
+        <v>644</v>
       </c>
       <c r="J6" s="77" t="s">
         <v>170</v>
@@ -6054,28 +6033,28 @@
     </row>
     <row r="7" spans="1:11">
       <c r="B7" s="77" t="s">
-        <v>652</v>
+        <v>646</v>
       </c>
       <c r="D7" s="77" t="s">
-        <v>654</v>
+        <v>647</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>60</v>
       </c>
       <c r="H7" s="78" t="s">
-        <v>659</v>
+        <v>651</v>
       </c>
       <c r="I7" s="77" t="s">
-        <v>658</v>
+        <v>650</v>
       </c>
       <c r="J7" s="77" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="K7" s="7"/>
     </row>
     <row r="8" spans="1:11" ht="29">
       <c r="B8" s="18" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="D8" s="77" t="s">
         <v>171</v>
@@ -6084,10 +6063,10 @@
         <v>60</v>
       </c>
       <c r="H8" s="77" t="s">
-        <v>637</v>
+        <v>632</v>
       </c>
       <c r="I8" s="80" t="s">
-        <v>660</v>
+        <v>652</v>
       </c>
       <c r="J8" s="77" t="s">
         <v>172</v>
@@ -6114,13 +6093,13 @@
         <v>63</v>
       </c>
       <c r="J9" s="77" t="s">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="K9" s="7"/>
     </row>
     <row r="10" spans="1:11" s="24" customFormat="1">
       <c r="A10" s="26" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="B10" s="25" t="s">
         <v>80</v>
@@ -6129,7 +6108,7 @@
         <v>2</v>
       </c>
       <c r="D10" s="25" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="E10" s="25" t="s">
         <v>60</v>
@@ -6147,7 +6126,7 @@
         <v>178</v>
       </c>
       <c r="J10" s="25" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="K10" s="24" t="s">
         <v>86</v>
@@ -6183,7 +6162,7 @@
         <v>178</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="K12" t="s">
         <v>88</v>
@@ -6201,7 +6180,7 @@
         <v>178</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="K13" t="s">
         <v>89</v>
@@ -6237,7 +6216,7 @@
         <v>178</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="K15" t="s">
         <v>91</v>
@@ -6255,7 +6234,7 @@
         <v>178</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="K16" t="s">
         <v>92</v>
@@ -6291,7 +6270,7 @@
         <v>178</v>
       </c>
       <c r="J18" s="4" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="K18" t="s">
         <v>94</v>
@@ -6309,7 +6288,7 @@
         <v>178</v>
       </c>
       <c r="J19" s="4" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="K19" t="s">
         <v>95</v>
@@ -6339,7 +6318,7 @@
         <v>62</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="J20" s="4" t="s">
         <v>99</v>
@@ -6357,7 +6336,7 @@
         <v>82</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="J21" s="4" t="s">
         <v>100</v>
@@ -6375,10 +6354,10 @@
         <v>82</v>
       </c>
       <c r="I22" s="4" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="J22" s="4" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="K22" t="s">
         <v>104</v>
@@ -6393,7 +6372,7 @@
         <v>82</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="J23" s="4" t="s">
         <v>101</v>
@@ -6410,7 +6389,7 @@
         <v>168</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="E24" s="8" t="s">
         <v>60</v>
@@ -6428,7 +6407,7 @@
         <v>178</v>
       </c>
       <c r="J24" s="22" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="K24" s="4"/>
     </row>
@@ -6444,7 +6423,7 @@
         <v>178</v>
       </c>
       <c r="J25" s="22" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="K25" s="4"/>
     </row>
@@ -6460,7 +6439,7 @@
         <v>178</v>
       </c>
       <c r="J26" s="22" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="K26" s="4"/>
     </row>
@@ -6476,7 +6455,7 @@
         <v>178</v>
       </c>
       <c r="J27" s="22" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="K27" s="4"/>
     </row>
@@ -6492,7 +6471,7 @@
         <v>178</v>
       </c>
       <c r="J28" s="22" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="K28" s="4"/>
     </row>
@@ -6520,7 +6499,7 @@
         <v>72</v>
       </c>
       <c r="J29" s="4" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="K29" t="s">
         <v>76</v>
@@ -6573,7 +6552,7 @@
     </row>
     <row r="33" spans="1:11" s="24" customFormat="1">
       <c r="A33" s="26" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="B33" s="25" t="s">
         <v>106</v>
@@ -6597,7 +6576,7 @@
         <v>62</v>
       </c>
       <c r="I33" s="4" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="J33" s="25" t="s">
         <v>109</v>
@@ -6615,10 +6594,10 @@
         <v>82</v>
       </c>
       <c r="I34" s="4" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="J34" s="4" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="K34" t="s">
         <v>113</v>
@@ -6633,10 +6612,10 @@
         <v>82</v>
       </c>
       <c r="I35" s="4" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="J35" s="4" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="K35" t="s">
         <v>114</v>
@@ -6651,7 +6630,7 @@
         <v>82</v>
       </c>
       <c r="I36" s="4" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="J36" s="4" t="s">
         <v>110</v>
@@ -6669,7 +6648,7 @@
         <v>82</v>
       </c>
       <c r="I37" s="4" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="J37" s="4" t="s">
         <v>111</v>
@@ -6689,7 +6668,7 @@
         <v>1</v>
       </c>
       <c r="D38" s="25" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="E38" s="25" t="s">
         <v>125</v>
@@ -6698,16 +6677,16 @@
         <v>175</v>
       </c>
       <c r="G38" s="25" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="H38" s="25" t="s">
         <v>62</v>
       </c>
       <c r="I38" s="4" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="J38" s="25" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="K38" s="24" t="s">
         <v>129</v>
@@ -6719,13 +6698,13 @@
       <c r="C39" s="4"/>
       <c r="D39" s="4"/>
       <c r="G39" s="25" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="I39" s="4" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="J39" s="4" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="K39" t="s">
         <v>130</v>
@@ -6737,13 +6716,13 @@
       <c r="C40" s="4"/>
       <c r="D40" s="4"/>
       <c r="G40" s="25" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="I40" s="4" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="J40" s="4" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="K40" t="s">
         <v>131</v>
@@ -6755,13 +6734,13 @@
       <c r="C41" s="4"/>
       <c r="D41" s="4"/>
       <c r="G41" s="25" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="I41" s="4" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="J41" s="4" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="K41" t="s">
         <v>132</v>
@@ -6773,13 +6752,13 @@
       <c r="C42" s="4"/>
       <c r="D42" s="4"/>
       <c r="G42" s="25" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="I42" s="4" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="J42" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K42" t="s">
         <v>133</v>
@@ -6791,13 +6770,13 @@
       <c r="C43" s="4"/>
       <c r="D43" s="4"/>
       <c r="G43" s="25" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="I43" s="4" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="J43" s="4" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="K43" t="s">
         <v>134</v>
@@ -6809,13 +6788,13 @@
       <c r="C44" s="4"/>
       <c r="D44" s="4"/>
       <c r="G44" s="25" t="s">
+        <v>378</v>
+      </c>
+      <c r="I44" s="4" t="s">
+        <v>397</v>
+      </c>
+      <c r="J44" s="4" t="s">
         <v>382</v>
-      </c>
-      <c r="I44" s="4" t="s">
-        <v>401</v>
-      </c>
-      <c r="J44" s="4" t="s">
-        <v>386</v>
       </c>
       <c r="K44" t="s">
         <v>135</v>
@@ -6827,13 +6806,13 @@
       <c r="C45" s="4"/>
       <c r="D45" s="4"/>
       <c r="G45" s="25" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="I45" s="4" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="J45" s="4" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="K45" t="s">
         <v>136</v>
@@ -6845,13 +6824,13 @@
       <c r="C46" s="4"/>
       <c r="D46" s="4"/>
       <c r="G46" s="25" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="I46" s="4" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="J46" s="4" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="K46" t="s">
         <v>137</v>
@@ -6863,13 +6842,13 @@
       <c r="C47" s="4"/>
       <c r="D47" s="4"/>
       <c r="G47" s="25" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="I47" s="4" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="J47" s="4" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="K47" t="s">
         <v>138</v>
@@ -6899,10 +6878,10 @@
         <v>62</v>
       </c>
       <c r="I48" s="4" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="J48" s="4" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="K48" t="s">
         <v>142</v>
@@ -6917,10 +6896,10 @@
         <v>126</v>
       </c>
       <c r="I49" s="4" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="J49" s="4" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="K49" t="s">
         <v>143</v>
@@ -6935,10 +6914,10 @@
         <v>126</v>
       </c>
       <c r="I50" s="4" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="J50" s="4" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="K50" t="s">
         <v>144</v>
@@ -6953,10 +6932,10 @@
         <v>126</v>
       </c>
       <c r="I51" s="4" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="J51" s="4" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="K51" t="s">
         <v>145</v>
@@ -6971,10 +6950,10 @@
         <v>126</v>
       </c>
       <c r="I52" s="4" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="J52" s="4" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="K52" t="s">
         <v>146</v>
@@ -6989,10 +6968,10 @@
         <v>126</v>
       </c>
       <c r="I53" s="4" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="J53" s="4" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="K53" t="s">
         <v>147</v>
@@ -7022,10 +7001,10 @@
         <v>62</v>
       </c>
       <c r="I54" s="4" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="J54" s="4" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="K54" t="s">
         <v>152</v>
@@ -7040,10 +7019,10 @@
         <v>151</v>
       </c>
       <c r="I55" s="4" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="J55" s="4" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="K55" t="s">
         <v>153</v>
@@ -7051,7 +7030,7 @@
     </row>
     <row r="56" spans="1:11" s="24" customFormat="1">
       <c r="A56" s="26" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="B56" s="25" t="s">
         <v>176</v>
@@ -7066,19 +7045,19 @@
         <v>60</v>
       </c>
       <c r="F56" s="25" t="s">
+        <v>117</v>
+      </c>
+      <c r="G56" s="25" t="s">
         <v>154</v>
-      </c>
-      <c r="G56" s="25" t="s">
-        <v>117</v>
       </c>
       <c r="H56" s="25" t="s">
         <v>62</v>
       </c>
       <c r="I56" s="25" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="J56" s="25" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="K56" s="24" t="s">
         <v>156</v>
@@ -7090,13 +7069,13 @@
       <c r="C57" s="4"/>
       <c r="D57" s="4"/>
       <c r="G57" s="25" t="s">
-        <v>117</v>
+        <v>154</v>
       </c>
       <c r="I57" s="25" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="J57" s="4" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="K57" t="s">
         <v>157</v>
@@ -7108,13 +7087,13 @@
       <c r="C58" s="4"/>
       <c r="D58" s="4"/>
       <c r="G58" s="25" t="s">
-        <v>117</v>
+        <v>154</v>
       </c>
       <c r="I58" s="25" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="J58" s="4" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="K58" t="s">
         <v>158</v>
@@ -7126,13 +7105,13 @@
       <c r="C59" s="4"/>
       <c r="D59" s="4"/>
       <c r="G59" s="25" t="s">
-        <v>117</v>
+        <v>154</v>
       </c>
       <c r="I59" s="25" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="J59" s="4" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="K59" t="s">
         <v>159</v>
@@ -7144,10 +7123,10 @@
       <c r="C60" s="4"/>
       <c r="D60" s="4"/>
       <c r="G60" s="25" t="s">
-        <v>117</v>
+        <v>154</v>
       </c>
       <c r="I60" s="25" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="J60" s="4" t="s">
         <v>155</v>
@@ -7197,7 +7176,7 @@
     </row>
     <row r="65" spans="1:3" ht="64">
       <c r="B65" s="22" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="C65" s="8" t="s">
         <v>121</v>
@@ -7263,7 +7242,7 @@
     </row>
     <row r="73" spans="1:3">
       <c r="B73" s="8" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C73" s="8" t="s">
         <v>121</v>
@@ -7271,7 +7250,7 @@
     </row>
     <row r="74" spans="1:3" ht="35" customHeight="1">
       <c r="B74" s="22" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
     </row>
   </sheetData>
@@ -7293,7 +7272,7 @@
   <sheetData>
     <row r="1" spans="1:12" ht="17" thickBot="1">
       <c r="A1" s="94" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="B1" s="94"/>
       <c r="C1" s="94"/>
@@ -7309,7 +7288,7 @@
     </row>
     <row r="2" spans="1:12" ht="17" thickBot="1">
       <c r="A2" s="68" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="B2" s="16" t="s">
         <v>0</v>
@@ -7324,7 +7303,7 @@
         <v>55</v>
       </c>
       <c r="F2" s="16" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="G2" s="16" t="s">
         <v>56</v>
@@ -7342,15 +7321,15 @@
         <v>42</v>
       </c>
       <c r="L2" s="69" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="11" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="C3" s="6">
         <v>2</v>
@@ -7362,10 +7341,10 @@
         <v>60</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="H3" s="6" t="s">
         <v>61</v>
@@ -7374,19 +7353,19 @@
         <v>62</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>630</v>
+        <v>625</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="L3" s="6" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="4"/>
       <c r="B4" s="6" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="C4" s="6">
         <v>3</v>
@@ -7398,13 +7377,13 @@
         <v>60</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="I4" s="6" t="s">
         <v>63</v>
@@ -7413,10 +7392,10 @@
         <v>1</v>
       </c>
       <c r="K4" s="7" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="L4" s="6" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -7433,10 +7412,10 @@
         <v>2</v>
       </c>
       <c r="K5" s="7" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="L5" s="6" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -7453,10 +7432,10 @@
         <v>3</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="L6" s="6" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -7473,10 +7452,10 @@
         <v>4</v>
       </c>
       <c r="K7" s="7" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="L7" s="6" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -7493,10 +7472,10 @@
         <v>5</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="L8" s="6" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -7513,10 +7492,10 @@
         <v>6</v>
       </c>
       <c r="K9" s="7" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="L9" s="6" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -7533,16 +7512,16 @@
         <v>0</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="L10" s="6" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="A11" s="4"/>
       <c r="B11" s="6" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="C11" s="6">
         <v>2</v>
@@ -7554,10 +7533,10 @@
         <v>60</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="H11" s="6" t="s">
         <v>61</v>
@@ -7566,19 +7545,19 @@
         <v>62</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>630</v>
+        <v>625</v>
       </c>
       <c r="K11" s="7" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="L11" s="6" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
     </row>
     <row r="12" spans="1:12">
       <c r="A12" s="5"/>
       <c r="B12" s="5" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="C12" s="5">
         <v>1</v>
@@ -7590,49 +7569,49 @@
         <v>60</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="I12" s="5" t="s">
         <v>66</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="K12" s="7" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="L12" s="6" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
     </row>
     <row r="13" spans="1:12">
       <c r="A13" s="6"/>
       <c r="B13" s="6" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="C13" s="6">
         <v>1</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="E13" s="6" t="s">
         <v>60</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="I13" s="6" t="s">
         <v>62</v>
@@ -7641,10 +7620,10 @@
         <v>1</v>
       </c>
       <c r="K13" s="7" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="L13" s="6" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -7661,7 +7640,7 @@
         <v>2</v>
       </c>
       <c r="K14" s="7" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="L14" s="6"/>
     </row>
@@ -7679,7 +7658,7 @@
         <v>3</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="L15" s="6"/>
     </row>
@@ -7697,7 +7676,7 @@
         <v>4</v>
       </c>
       <c r="K16" s="7" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="L16" s="6" t="s">
         <v>121</v>
@@ -7717,7 +7696,7 @@
         <v>5</v>
       </c>
       <c r="K17" s="7" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="L17" s="6" t="s">
         <v>121</v>
@@ -7737,7 +7716,7 @@
         <v>6</v>
       </c>
       <c r="K18" s="7" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="L18" s="6" t="s">
         <v>121</v>
@@ -7757,7 +7736,7 @@
         <v>7</v>
       </c>
       <c r="K19" s="7" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="L19" s="6" t="s">
         <v>121</v>
@@ -7777,7 +7756,7 @@
         <v>8</v>
       </c>
       <c r="K20" s="7" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
       <c r="L20" s="6" t="s">
         <v>121</v>
@@ -7797,7 +7776,7 @@
         <v>9</v>
       </c>
       <c r="K21" s="7" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="L21" s="6" t="s">
         <v>121</v>
@@ -7817,7 +7796,7 @@
         <v>10</v>
       </c>
       <c r="K22" s="7" t="s">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="L22" s="6" t="s">
         <v>121</v>
@@ -7837,29 +7816,29 @@
         <v>0</v>
       </c>
       <c r="K23" s="7" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="L23" s="6"/>
     </row>
     <row r="24" spans="1:12">
       <c r="A24" s="4"/>
       <c r="B24" s="5" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="C24" s="5">
         <v>1</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="E24" s="5" t="s">
         <v>60</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="H24" s="5" t="s">
         <v>66</v>
@@ -7868,19 +7847,19 @@
         <v>66</v>
       </c>
       <c r="J24" s="5" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="K24" s="7" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="L24" s="6" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
     </row>
     <row r="25" spans="1:12">
       <c r="A25" s="4"/>
       <c r="B25" s="6" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="C25" s="6">
         <v>1</v>
@@ -7892,13 +7871,13 @@
         <v>60</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="I25" s="6" t="s">
         <v>63</v>
@@ -7907,10 +7886,10 @@
         <v>1</v>
       </c>
       <c r="K25" s="7" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="L25" s="6" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
     </row>
     <row r="26" spans="1:12">
@@ -7927,10 +7906,10 @@
         <v>2</v>
       </c>
       <c r="K26" s="7" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="L26" s="6" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
     </row>
     <row r="27" spans="1:12">
@@ -7947,10 +7926,10 @@
         <v>3</v>
       </c>
       <c r="K27" s="7" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="L27" s="6" t="s">
-        <v>496</v>
+        <v>491</v>
       </c>
     </row>
     <row r="28" spans="1:12">
@@ -7967,10 +7946,10 @@
         <v>4</v>
       </c>
       <c r="K28" s="7" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="L28" s="6" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
     </row>
     <row r="29" spans="1:12">
@@ -7987,10 +7966,10 @@
         <v>5</v>
       </c>
       <c r="K29" s="7" t="s">
-        <v>499</v>
+        <v>494</v>
       </c>
       <c r="L29" s="6" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
     </row>
     <row r="30" spans="1:12">
@@ -8007,10 +7986,10 @@
         <v>6</v>
       </c>
       <c r="K30" s="7" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="L30" s="6" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
     </row>
     <row r="31" spans="1:12">
@@ -8027,10 +8006,10 @@
         <v>7</v>
       </c>
       <c r="K31" s="7" t="s">
-        <v>503</v>
+        <v>498</v>
       </c>
       <c r="L31" s="6" t="s">
-        <v>504</v>
+        <v>499</v>
       </c>
     </row>
     <row r="32" spans="1:12">
@@ -8047,10 +8026,10 @@
         <v>8</v>
       </c>
       <c r="K32" s="7" t="s">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="L32" s="6" t="s">
-        <v>506</v>
+        <v>501</v>
       </c>
     </row>
     <row r="33" spans="1:12">
@@ -8067,10 +8046,10 @@
         <v>9</v>
       </c>
       <c r="K33" s="7" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="L33" s="6" t="s">
-        <v>508</v>
+        <v>503</v>
       </c>
     </row>
     <row r="34" spans="1:12">
@@ -8087,10 +8066,10 @@
         <v>10</v>
       </c>
       <c r="K34" s="7" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="L34" s="6" t="s">
-        <v>510</v>
+        <v>505</v>
       </c>
     </row>
     <row r="35" spans="1:12">
@@ -8107,10 +8086,10 @@
         <v>11</v>
       </c>
       <c r="K35" s="7" t="s">
-        <v>511</v>
+        <v>506</v>
       </c>
       <c r="L35" s="6" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
     </row>
     <row r="36" spans="1:12">
@@ -8127,10 +8106,10 @@
         <v>12</v>
       </c>
       <c r="K36" s="7" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="L36" s="6" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
     </row>
     <row r="37" spans="1:12">
@@ -8147,10 +8126,10 @@
         <v>13</v>
       </c>
       <c r="K37" s="70" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
       <c r="L37" s="6" t="s">
-        <v>516</v>
+        <v>511</v>
       </c>
     </row>
     <row r="38" spans="1:12">
@@ -8167,10 +8146,10 @@
         <v>14</v>
       </c>
       <c r="K38" s="70" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="L38" s="6" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
     </row>
     <row r="39" spans="1:12">
@@ -8187,10 +8166,10 @@
         <v>15</v>
       </c>
       <c r="K39" s="70" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="L39" s="6" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
     </row>
     <row r="40" spans="1:12">
@@ -8207,10 +8186,10 @@
         <v>16</v>
       </c>
       <c r="K40" s="70" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="L40" s="6" t="s">
-        <v>522</v>
+        <v>517</v>
       </c>
     </row>
     <row r="41" spans="1:12">
@@ -8227,10 +8206,10 @@
         <v>17</v>
       </c>
       <c r="K41" s="70" t="s">
-        <v>523</v>
+        <v>518</v>
       </c>
       <c r="L41" s="6" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
     </row>
     <row r="42" spans="1:12" ht="32">
@@ -8247,10 +8226,10 @@
         <v>18</v>
       </c>
       <c r="K42" s="70" t="s">
-        <v>525</v>
+        <v>520</v>
       </c>
       <c r="L42" s="6" t="s">
-        <v>526</v>
+        <v>521</v>
       </c>
     </row>
     <row r="43" spans="1:12">
@@ -8267,10 +8246,10 @@
         <v>19</v>
       </c>
       <c r="K43" s="70" t="s">
-        <v>527</v>
+        <v>522</v>
       </c>
       <c r="L43" s="6" t="s">
-        <v>528</v>
+        <v>523</v>
       </c>
     </row>
     <row r="44" spans="1:12" ht="32">
@@ -8287,10 +8266,10 @@
         <v>20</v>
       </c>
       <c r="K44" s="70" t="s">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="L44" s="6" t="s">
-        <v>530</v>
+        <v>525</v>
       </c>
     </row>
     <row r="45" spans="1:12" ht="32">
@@ -8310,28 +8289,28 @@
         <v>68</v>
       </c>
       <c r="L45" s="6" t="s">
-        <v>531</v>
+        <v>526</v>
       </c>
     </row>
     <row r="46" spans="1:12">
       <c r="A46" s="6"/>
       <c r="B46" s="6" t="s">
-        <v>532</v>
+        <v>527</v>
       </c>
       <c r="C46" s="6">
         <v>1</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>60</v>
       </c>
       <c r="F46" s="6" t="s">
-        <v>533</v>
+        <v>528</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>534</v>
+        <v>529</v>
       </c>
       <c r="H46" s="6" t="s">
         <v>66</v>
@@ -8340,19 +8319,19 @@
         <v>66</v>
       </c>
       <c r="J46" s="6" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="K46" s="70" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="L46" s="6" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
     </row>
     <row r="47" spans="1:12">
       <c r="A47" s="4"/>
       <c r="B47" s="6" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="C47" s="6">
         <v>3</v>
@@ -8364,13 +8343,13 @@
         <v>60</v>
       </c>
       <c r="F47" s="6" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="G47" s="6" t="s">
-        <v>536</v>
+        <v>531</v>
       </c>
       <c r="H47" s="6" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="I47" s="6" t="s">
         <v>63</v>
@@ -8379,10 +8358,10 @@
         <v>1</v>
       </c>
       <c r="K47" s="70" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="L47" s="6" t="s">
-        <v>537</v>
+        <v>532</v>
       </c>
     </row>
     <row r="48" spans="1:12">
@@ -8399,10 +8378,10 @@
         <v>2</v>
       </c>
       <c r="K48" s="70" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="L48" s="6" t="s">
-        <v>538</v>
+        <v>533</v>
       </c>
     </row>
     <row r="49" spans="1:12">
@@ -8419,10 +8398,10 @@
         <v>3</v>
       </c>
       <c r="K49" s="70" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="L49" s="6" t="s">
-        <v>539</v>
+        <v>534</v>
       </c>
     </row>
     <row r="50" spans="1:12">
@@ -8439,10 +8418,10 @@
         <v>4</v>
       </c>
       <c r="K50" s="70" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="L50" s="6" t="s">
-        <v>540</v>
+        <v>535</v>
       </c>
     </row>
     <row r="51" spans="1:12">
@@ -8459,10 +8438,10 @@
         <v>5</v>
       </c>
       <c r="K51" s="70" t="s">
-        <v>499</v>
+        <v>494</v>
       </c>
       <c r="L51" s="6" t="s">
-        <v>541</v>
+        <v>536</v>
       </c>
     </row>
     <row r="52" spans="1:12">
@@ -8479,10 +8458,10 @@
         <v>6</v>
       </c>
       <c r="K52" s="70" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="L52" s="6" t="s">
-        <v>542</v>
+        <v>537</v>
       </c>
     </row>
     <row r="53" spans="1:12">
@@ -8499,10 +8478,10 @@
         <v>7</v>
       </c>
       <c r="K53" s="70" t="s">
-        <v>503</v>
+        <v>498</v>
       </c>
       <c r="L53" s="6" t="s">
-        <v>543</v>
+        <v>538</v>
       </c>
     </row>
     <row r="54" spans="1:12">
@@ -8519,10 +8498,10 @@
         <v>8</v>
       </c>
       <c r="K54" s="70" t="s">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="L54" s="6" t="s">
-        <v>544</v>
+        <v>539</v>
       </c>
     </row>
     <row r="55" spans="1:12">
@@ -8539,10 +8518,10 @@
         <v>9</v>
       </c>
       <c r="K55" s="70" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="L55" s="6" t="s">
-        <v>545</v>
+        <v>540</v>
       </c>
     </row>
     <row r="56" spans="1:12">
@@ -8559,10 +8538,10 @@
         <v>10</v>
       </c>
       <c r="K56" s="70" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="L56" s="6" t="s">
-        <v>546</v>
+        <v>541</v>
       </c>
     </row>
     <row r="57" spans="1:12" ht="32">
@@ -8579,10 +8558,10 @@
         <v>11</v>
       </c>
       <c r="K57" s="70" t="s">
-        <v>511</v>
+        <v>506</v>
       </c>
       <c r="L57" s="6" t="s">
-        <v>547</v>
+        <v>542</v>
       </c>
     </row>
     <row r="58" spans="1:12" ht="32">
@@ -8599,10 +8578,10 @@
         <v>12</v>
       </c>
       <c r="K58" s="70" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="L58" s="6" t="s">
-        <v>548</v>
+        <v>543</v>
       </c>
     </row>
     <row r="59" spans="1:12">
@@ -8619,10 +8598,10 @@
         <v>13</v>
       </c>
       <c r="K59" s="70" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
       <c r="L59" s="6" t="s">
-        <v>549</v>
+        <v>544</v>
       </c>
     </row>
     <row r="60" spans="1:12">
@@ -8639,10 +8618,10 @@
         <v>14</v>
       </c>
       <c r="K60" s="70" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="L60" s="6" t="s">
-        <v>550</v>
+        <v>545</v>
       </c>
     </row>
     <row r="61" spans="1:12">
@@ -8659,10 +8638,10 @@
         <v>15</v>
       </c>
       <c r="K61" s="70" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="L61" s="6" t="s">
-        <v>551</v>
+        <v>546</v>
       </c>
     </row>
     <row r="62" spans="1:12">
@@ -8679,10 +8658,10 @@
         <v>16</v>
       </c>
       <c r="K62" s="70" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="L62" s="6" t="s">
-        <v>552</v>
+        <v>547</v>
       </c>
     </row>
     <row r="63" spans="1:12">
@@ -8699,10 +8678,10 @@
         <v>17</v>
       </c>
       <c r="K63" s="70" t="s">
-        <v>523</v>
+        <v>518</v>
       </c>
       <c r="L63" s="6" t="s">
-        <v>553</v>
+        <v>548</v>
       </c>
     </row>
     <row r="64" spans="1:12" ht="32">
@@ -8719,10 +8698,10 @@
         <v>18</v>
       </c>
       <c r="K64" s="70" t="s">
-        <v>525</v>
+        <v>520</v>
       </c>
       <c r="L64" s="6" t="s">
-        <v>554</v>
+        <v>549</v>
       </c>
     </row>
     <row r="65" spans="1:12">
@@ -8739,10 +8718,10 @@
         <v>19</v>
       </c>
       <c r="K65" s="70" t="s">
-        <v>527</v>
+        <v>522</v>
       </c>
       <c r="L65" s="6" t="s">
-        <v>555</v>
+        <v>550</v>
       </c>
     </row>
     <row r="66" spans="1:12" ht="32">
@@ -8759,10 +8738,10 @@
         <v>20</v>
       </c>
       <c r="K66" s="70" t="s">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="L66" s="6" t="s">
-        <v>556</v>
+        <v>551</v>
       </c>
     </row>
     <row r="67" spans="1:12" ht="32">
@@ -8782,28 +8761,28 @@
         <v>68</v>
       </c>
       <c r="L67" s="6" t="s">
-        <v>557</v>
+        <v>552</v>
       </c>
     </row>
     <row r="68" spans="1:12">
       <c r="A68" s="5"/>
       <c r="B68" s="5" t="s">
-        <v>558</v>
+        <v>553</v>
       </c>
       <c r="C68" s="6">
         <v>3</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="E68" s="5" t="s">
         <v>60</v>
       </c>
       <c r="F68" s="5" t="s">
-        <v>559</v>
+        <v>554</v>
       </c>
       <c r="G68" s="5" t="s">
-        <v>560</v>
+        <v>555</v>
       </c>
       <c r="H68" s="5" t="s">
         <v>66</v>
@@ -8812,37 +8791,37 @@
         <v>66</v>
       </c>
       <c r="J68" s="5" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="K68" s="70" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="L68" s="6" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
     </row>
     <row r="69" spans="1:12">
       <c r="A69" s="6"/>
       <c r="B69" s="6" t="s">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="C69" s="6">
         <v>3</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="E69" s="6" t="s">
         <v>60</v>
       </c>
       <c r="F69" s="6" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="G69" s="6" t="s">
-        <v>562</v>
+        <v>557</v>
       </c>
       <c r="H69" s="6" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="I69" s="6" t="s">
         <v>63</v>
@@ -8851,10 +8830,10 @@
         <v>1</v>
       </c>
       <c r="K69" s="7" t="s">
-        <v>563</v>
+        <v>558</v>
       </c>
       <c r="L69" s="6" t="s">
-        <v>564</v>
+        <v>559</v>
       </c>
     </row>
     <row r="70" spans="1:12">
@@ -8871,10 +8850,10 @@
         <v>2</v>
       </c>
       <c r="K70" s="7" t="s">
-        <v>565</v>
+        <v>560</v>
       </c>
       <c r="L70" s="6" t="s">
-        <v>566</v>
+        <v>561</v>
       </c>
     </row>
     <row r="71" spans="1:12">
@@ -8891,10 +8870,10 @@
         <v>3</v>
       </c>
       <c r="K71" s="7" t="s">
-        <v>567</v>
+        <v>562</v>
       </c>
       <c r="L71" s="6" t="s">
-        <v>568</v>
+        <v>563</v>
       </c>
     </row>
     <row r="72" spans="1:12">
@@ -8911,10 +8890,10 @@
         <v>4</v>
       </c>
       <c r="K72" s="7" t="s">
-        <v>569</v>
+        <v>564</v>
       </c>
       <c r="L72" s="6" t="s">
-        <v>570</v>
+        <v>565</v>
       </c>
     </row>
     <row r="73" spans="1:12">
@@ -8931,10 +8910,10 @@
         <v>5</v>
       </c>
       <c r="K73" s="7" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="L73" s="6" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
     </row>
     <row r="74" spans="1:12">
@@ -8951,15 +8930,15 @@
         <v>0</v>
       </c>
       <c r="K74" s="10" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="L74" s="9" t="s">
-        <v>573</v>
+        <v>568</v>
       </c>
     </row>
     <row r="75" spans="1:12">
       <c r="A75" s="12" t="s">
-        <v>574</v>
+        <v>569</v>
       </c>
       <c r="B75" s="6" t="s">
         <v>69</v>
@@ -8974,7 +8953,7 @@
         <v>60</v>
       </c>
       <c r="F75" s="6" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="G75" s="6" t="s">
         <v>71</v>
@@ -8987,7 +8966,7 @@
         <v>178</v>
       </c>
       <c r="K75" s="7" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="L75" s="6" t="s">
         <v>76</v>
@@ -9062,13 +9041,13 @@
         <v>2</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>576</v>
+        <v>571</v>
       </c>
       <c r="E79" s="6" t="s">
         <v>60</v>
       </c>
       <c r="F79" s="6" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="G79" s="6" t="s">
         <v>81</v>
@@ -9083,7 +9062,7 @@
         <v>178</v>
       </c>
       <c r="K79" s="7" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
       <c r="L79" s="7" t="s">
         <v>86</v>
@@ -9123,7 +9102,7 @@
         <v>178</v>
       </c>
       <c r="K81" s="7" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="L81" s="7" t="s">
         <v>88</v>
@@ -9143,7 +9122,7 @@
         <v>178</v>
       </c>
       <c r="K82" s="7" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
       <c r="L82" s="7" t="s">
         <v>89</v>
@@ -9183,7 +9162,7 @@
         <v>178</v>
       </c>
       <c r="K84" s="7" t="s">
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="L84" s="7" t="s">
         <v>91</v>
@@ -9203,7 +9182,7 @@
         <v>178</v>
       </c>
       <c r="K85" s="7" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
       <c r="L85" s="7" t="s">
         <v>92</v>
@@ -9243,7 +9222,7 @@
         <v>178</v>
       </c>
       <c r="K87" s="7" t="s">
-        <v>582</v>
+        <v>577</v>
       </c>
       <c r="L87" s="7" t="s">
         <v>94</v>
@@ -9263,7 +9242,7 @@
         <v>178</v>
       </c>
       <c r="K88" s="7" t="s">
-        <v>583</v>
+        <v>578</v>
       </c>
       <c r="L88" s="7" t="s">
         <v>95</v>
@@ -9284,7 +9263,7 @@
         <v>60</v>
       </c>
       <c r="F89" s="6" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="G89" s="6" t="s">
         <v>98</v>
@@ -9296,7 +9275,7 @@
         <v>62</v>
       </c>
       <c r="J89" s="6" t="s">
-        <v>584</v>
+        <v>579</v>
       </c>
       <c r="K89" s="7" t="s">
         <v>99</v>
@@ -9316,7 +9295,7 @@
       <c r="H90" s="6"/>
       <c r="I90" s="6"/>
       <c r="J90" s="6" t="s">
-        <v>584</v>
+        <v>579</v>
       </c>
       <c r="K90" s="7" t="s">
         <v>100</v>
@@ -9336,10 +9315,10 @@
       <c r="H91" s="6"/>
       <c r="I91" s="6"/>
       <c r="J91" s="6" t="s">
-        <v>584</v>
+        <v>579</v>
       </c>
       <c r="K91" s="7" t="s">
-        <v>585</v>
+        <v>580</v>
       </c>
       <c r="L91" s="6" t="s">
         <v>104</v>
@@ -9356,7 +9335,7 @@
       <c r="H92" s="6"/>
       <c r="I92" s="6"/>
       <c r="J92" s="6" t="s">
-        <v>584</v>
+        <v>579</v>
       </c>
       <c r="K92" s="7" t="s">
         <v>101</v>
@@ -9380,7 +9359,7 @@
         <v>60</v>
       </c>
       <c r="F93" s="6" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="G93" s="6" t="s">
         <v>108</v>
@@ -9392,7 +9371,7 @@
         <v>62</v>
       </c>
       <c r="J93" s="6" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="K93" s="7" t="s">
         <v>109</v>
@@ -9412,10 +9391,10 @@
       <c r="H94" s="6"/>
       <c r="I94" s="6"/>
       <c r="J94" s="6" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="K94" s="7" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="L94" s="7" t="s">
         <v>113</v>
@@ -9432,10 +9411,10 @@
       <c r="H95" s="6"/>
       <c r="I95" s="6"/>
       <c r="J95" s="6" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="K95" s="7" t="s">
-        <v>587</v>
+        <v>582</v>
       </c>
       <c r="L95" s="7" t="s">
         <v>114</v>
@@ -9452,7 +9431,7 @@
       <c r="H96" s="6"/>
       <c r="I96" s="6"/>
       <c r="J96" s="6" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="K96" s="7" t="s">
         <v>110</v>
@@ -9472,7 +9451,7 @@
       <c r="H97" s="6"/>
       <c r="I97" s="6"/>
       <c r="J97" s="6" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="K97" s="7" t="s">
         <v>111</v>
@@ -9483,7 +9462,7 @@
     </row>
     <row r="98" spans="1:12">
       <c r="A98" s="11" t="s">
-        <v>588</v>
+        <v>583</v>
       </c>
       <c r="B98" s="6" t="s">
         <v>51</v>
@@ -9498,7 +9477,7 @@
         <v>60</v>
       </c>
       <c r="F98" s="6" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="G98" s="6" t="s">
         <v>53</v>
@@ -9516,7 +9495,7 @@
         <v>119</v>
       </c>
       <c r="L98" s="7" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
     </row>
     <row r="99" spans="1:12">
@@ -9534,7 +9513,7 @@
         <v>60</v>
       </c>
       <c r="F99" s="6" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="G99" s="6" t="s">
         <v>120</v>
@@ -9552,7 +9531,7 @@
         <v>122</v>
       </c>
       <c r="L99" s="6" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
     </row>
     <row r="100" spans="1:12">
@@ -9605,7 +9584,7 @@
         <v>0</v>
       </c>
       <c r="K102" s="10" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="L102" s="9"/>
     </row>
@@ -9620,7 +9599,7 @@
         <v>1</v>
       </c>
       <c r="D103" s="6" t="s">
-        <v>590</v>
+        <v>585</v>
       </c>
       <c r="E103" s="6" t="s">
         <v>125</v>
@@ -9630,16 +9609,16 @@
         <v>175</v>
       </c>
       <c r="H103" s="6" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="I103" s="6" t="s">
         <v>62</v>
       </c>
       <c r="J103" s="13" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="K103" s="14" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="L103" s="14" t="s">
         <v>129</v>
@@ -9656,10 +9635,10 @@
       <c r="H104" s="6"/>
       <c r="I104" s="6"/>
       <c r="J104" s="6" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="K104" s="7" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="L104" s="7" t="s">
         <v>130</v>
@@ -9676,10 +9655,10 @@
       <c r="H105" s="6"/>
       <c r="I105" s="6"/>
       <c r="J105" s="6" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="K105" s="7" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="L105" s="7" t="s">
         <v>131</v>
@@ -9696,10 +9675,10 @@
       <c r="H106" s="6"/>
       <c r="I106" s="6"/>
       <c r="J106" s="6" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="K106" s="7" t="s">
-        <v>595</v>
+        <v>590</v>
       </c>
       <c r="L106" s="7" t="s">
         <v>132</v>
@@ -9716,10 +9695,10 @@
       <c r="H107" s="6"/>
       <c r="I107" s="6"/>
       <c r="J107" s="6" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="K107" s="7" t="s">
-        <v>596</v>
+        <v>591</v>
       </c>
       <c r="L107" s="7" t="s">
         <v>133</v>
@@ -9736,10 +9715,10 @@
       <c r="H108" s="6"/>
       <c r="I108" s="6"/>
       <c r="J108" s="6" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="K108" s="7" t="s">
-        <v>597</v>
+        <v>592</v>
       </c>
       <c r="L108" s="7" t="s">
         <v>134</v>
@@ -9756,10 +9735,10 @@
       <c r="H109" s="6"/>
       <c r="I109" s="6"/>
       <c r="J109" s="6" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="K109" s="7" t="s">
-        <v>598</v>
+        <v>593</v>
       </c>
       <c r="L109" s="7" t="s">
         <v>135</v>
@@ -9776,10 +9755,10 @@
       <c r="H110" s="6"/>
       <c r="I110" s="6"/>
       <c r="J110" s="6" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="K110" s="7" t="s">
-        <v>599</v>
+        <v>594</v>
       </c>
       <c r="L110" s="7" t="s">
         <v>136</v>
@@ -9796,10 +9775,10 @@
       <c r="H111" s="6"/>
       <c r="I111" s="6"/>
       <c r="J111" s="6" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="K111" s="7" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="L111" s="7" t="s">
         <v>137</v>
@@ -9816,10 +9795,10 @@
       <c r="H112" s="6"/>
       <c r="I112" s="6"/>
       <c r="J112" s="6" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="K112" s="7" t="s">
-        <v>601</v>
+        <v>596</v>
       </c>
       <c r="L112" s="7" t="s">
         <v>138</v>
@@ -9850,10 +9829,10 @@
         <v>62</v>
       </c>
       <c r="J113" s="6" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="K113" s="7" t="s">
-        <v>602</v>
+        <v>597</v>
       </c>
       <c r="L113" s="7" t="s">
         <v>142</v>
@@ -9870,10 +9849,10 @@
       <c r="H114" s="6"/>
       <c r="I114" s="6"/>
       <c r="J114" s="6" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="K114" s="7" t="s">
-        <v>603</v>
+        <v>598</v>
       </c>
       <c r="L114" s="7" t="s">
         <v>143</v>
@@ -9890,10 +9869,10 @@
       <c r="H115" s="6"/>
       <c r="I115" s="6"/>
       <c r="J115" s="6" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="K115" s="7" t="s">
-        <v>604</v>
+        <v>599</v>
       </c>
       <c r="L115" s="7" t="s">
         <v>144</v>
@@ -9910,10 +9889,10 @@
       <c r="H116" s="6"/>
       <c r="I116" s="6"/>
       <c r="J116" s="6" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="K116" s="7" t="s">
-        <v>605</v>
+        <v>600</v>
       </c>
       <c r="L116" s="7" t="s">
         <v>145</v>
@@ -9930,10 +9909,10 @@
       <c r="H117" s="6"/>
       <c r="I117" s="6"/>
       <c r="J117" s="6" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="K117" s="7" t="s">
-        <v>606</v>
+        <v>601</v>
       </c>
       <c r="L117" s="7" t="s">
         <v>146</v>
@@ -9950,10 +9929,10 @@
       <c r="H118" s="6"/>
       <c r="I118" s="6"/>
       <c r="J118" s="6" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="K118" s="7" t="s">
-        <v>607</v>
+        <v>602</v>
       </c>
       <c r="L118" s="7" t="s">
         <v>147</v>
@@ -9984,10 +9963,10 @@
         <v>62</v>
       </c>
       <c r="J119" s="6" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="K119" s="7" t="s">
-        <v>608</v>
+        <v>603</v>
       </c>
       <c r="L119" s="7" t="s">
         <v>152</v>
@@ -10004,10 +9983,10 @@
       <c r="H120" s="9"/>
       <c r="I120" s="9"/>
       <c r="J120" s="6" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="K120" s="7" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="L120" s="7" t="s">
         <v>153</v>
@@ -10015,10 +9994,10 @@
     </row>
     <row r="121" spans="1:12">
       <c r="A121" s="11" t="s">
-        <v>610</v>
+        <v>605</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>611</v>
+        <v>606</v>
       </c>
       <c r="C121" s="4">
         <v>2</v>
@@ -10031,7 +10010,7 @@
       </c>
       <c r="F121" s="4"/>
       <c r="G121" s="4" t="s">
-        <v>612</v>
+        <v>607</v>
       </c>
       <c r="H121" s="4" t="s">
         <v>117</v>
@@ -10040,13 +10019,13 @@
         <v>62</v>
       </c>
       <c r="J121" s="6" t="s">
-        <v>613</v>
+        <v>608</v>
       </c>
       <c r="K121" s="7" t="s">
-        <v>614</v>
+        <v>609</v>
       </c>
       <c r="L121" s="7" t="s">
-        <v>615</v>
+        <v>610</v>
       </c>
     </row>
     <row r="122" spans="1:12">
@@ -10060,13 +10039,13 @@
       <c r="H122" s="4"/>
       <c r="I122" s="4"/>
       <c r="J122" s="6" t="s">
-        <v>613</v>
+        <v>608</v>
       </c>
       <c r="K122" s="7" t="s">
-        <v>616</v>
+        <v>611</v>
       </c>
       <c r="L122" s="7" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
     </row>
     <row r="123" spans="1:12">
@@ -10080,13 +10059,13 @@
       <c r="H123" s="4"/>
       <c r="I123" s="4"/>
       <c r="J123" s="6" t="s">
+        <v>608</v>
+      </c>
+      <c r="K123" s="7" t="s">
         <v>613</v>
       </c>
-      <c r="K123" s="7" t="s">
-        <v>618</v>
-      </c>
       <c r="L123" s="7" t="s">
-        <v>619</v>
+        <v>614</v>
       </c>
     </row>
     <row r="124" spans="1:12">
@@ -10100,13 +10079,13 @@
       <c r="H124" s="4"/>
       <c r="I124" s="4"/>
       <c r="J124" s="6" t="s">
-        <v>613</v>
+        <v>608</v>
       </c>
       <c r="K124" s="7" t="s">
-        <v>620</v>
+        <v>615</v>
       </c>
       <c r="L124" s="7" t="s">
-        <v>621</v>
+        <v>616</v>
       </c>
     </row>
     <row r="125" spans="1:12">
@@ -10120,13 +10099,13 @@
       <c r="H125" s="4"/>
       <c r="I125" s="4"/>
       <c r="J125" s="6" t="s">
-        <v>613</v>
+        <v>608</v>
       </c>
       <c r="K125" s="7" t="s">
-        <v>622</v>
+        <v>617</v>
       </c>
       <c r="L125" s="7" t="s">
-        <v>623</v>
+        <v>618</v>
       </c>
     </row>
     <row r="126" spans="1:12">
@@ -10140,13 +10119,13 @@
       <c r="H126" s="4"/>
       <c r="I126" s="4"/>
       <c r="J126" s="6" t="s">
-        <v>613</v>
+        <v>608</v>
       </c>
       <c r="K126" s="7" t="s">
-        <v>624</v>
+        <v>619</v>
       </c>
       <c r="L126" s="7" t="s">
-        <v>625</v>
+        <v>620</v>
       </c>
     </row>
     <row r="127" spans="1:12">
@@ -10174,10 +10153,10 @@
         <v>62</v>
       </c>
       <c r="J127" s="6" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="K127" s="71" t="s">
-        <v>626</v>
+        <v>621</v>
       </c>
       <c r="L127" s="71" t="s">
         <v>156</v>
@@ -10194,10 +10173,10 @@
       <c r="H128" s="4"/>
       <c r="I128" s="4"/>
       <c r="J128" s="6" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="K128" s="71" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="L128" s="71" t="s">
         <v>157</v>
@@ -10214,10 +10193,10 @@
       <c r="H129" s="4"/>
       <c r="I129" s="4"/>
       <c r="J129" s="6" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="K129" s="71" t="s">
-        <v>628</v>
+        <v>623</v>
       </c>
       <c r="L129" s="71" t="s">
         <v>158</v>
@@ -10234,10 +10213,10 @@
       <c r="H130" s="4"/>
       <c r="I130" s="4"/>
       <c r="J130" s="6" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="K130" s="71" t="s">
-        <v>629</v>
+        <v>624</v>
       </c>
       <c r="L130" s="71" t="s">
         <v>159</v>
@@ -10254,7 +10233,7 @@
       <c r="H131" s="15"/>
       <c r="I131" s="15"/>
       <c r="J131" s="6" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="K131" s="72" t="s">
         <v>155</v>
